--- a/research/traditional_assets/database/data/nigeria/nigeria_transportation.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_transportation.xlsx
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1633843262199065</v>
+        <v>0.1629256732412467</v>
       </c>
       <c r="C2">
-        <v>2.947789880416534</v>
+        <v>2.927812406310541</v>
       </c>
       <c r="D2">
-        <v>2.385789880416533</v>
+        <v>2.39513240631054</v>
       </c>
       <c r="E2">
-        <v>-0.202</v>
+        <v>-0.17268</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.02932</v>
       </c>
       <c r="G2">
         <v>0.5620000000000001</v>
@@ -1579,28 +1579,28 @@
         <v>0.745</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.001474796</v>
       </c>
       <c r="N2">
-        <v>0.745</v>
+        <v>0.743525204</v>
       </c>
       <c r="O2">
-        <v>0.2235</v>
+        <v>0.2230575612</v>
       </c>
       <c r="P2">
-        <v>0.5215</v>
+        <v>0.5204676428</v>
       </c>
       <c r="Q2">
-        <v>0.6294999999999999</v>
+        <v>0.6284676428</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1633843262199065</v>
+        <v>0.1642157305467138</v>
       </c>
       <c r="T2">
-        <v>0.8198499599185859</v>
+        <v>0.8256468788271011</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>505.1546112140256</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1629256732412467</v>
+        <v>0.162467020262587</v>
       </c>
       <c r="C3">
-        <v>2.927812406310541</v>
+        <v>2.907908388736133</v>
       </c>
       <c r="D3">
-        <v>2.39513240631054</v>
+        <v>2.404548388736133</v>
       </c>
       <c r="E3">
-        <v>-0.17268</v>
+        <v>-0.14336</v>
       </c>
       <c r="F3">
-        <v>0.02932</v>
+        <v>0.05864</v>
       </c>
       <c r="G3">
         <v>0.5620000000000001</v>
@@ -1661,28 +1661,28 @@
         <v>0.745</v>
       </c>
       <c r="M3">
-        <v>0.001474796</v>
+        <v>0.002949592</v>
       </c>
       <c r="N3">
-        <v>0.743525204</v>
+        <v>0.742050408</v>
       </c>
       <c r="O3">
-        <v>0.2230575612</v>
+        <v>0.2226151224</v>
       </c>
       <c r="P3">
-        <v>0.5204676428</v>
+        <v>0.5194352856</v>
       </c>
       <c r="Q3">
-        <v>0.6284676428</v>
+        <v>0.6274352855999999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1642157305467138</v>
+        <v>0.1650641023087622</v>
       </c>
       <c r="T3">
-        <v>0.8256468788271011</v>
+        <v>0.8315621022031371</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>505.1546112140256</v>
+        <v>252.5773056070128</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.162467020262587</v>
+        <v>0.1620083672839273</v>
       </c>
       <c r="C4">
-        <v>2.907908388736133</v>
+        <v>2.888078697451431</v>
       </c>
       <c r="D4">
-        <v>2.404548388736133</v>
+        <v>2.414038697451431</v>
       </c>
       <c r="E4">
-        <v>-0.14336</v>
+        <v>-0.11404</v>
       </c>
       <c r="F4">
-        <v>0.05864</v>
+        <v>0.08796</v>
       </c>
       <c r="G4">
         <v>0.5620000000000001</v>
@@ -1743,28 +1743,28 @@
         <v>0.745</v>
       </c>
       <c r="M4">
-        <v>0.002949592</v>
+        <v>0.004424388</v>
       </c>
       <c r="N4">
-        <v>0.742050408</v>
+        <v>0.740575612</v>
       </c>
       <c r="O4">
-        <v>0.2226151224</v>
+        <v>0.2221726836</v>
       </c>
       <c r="P4">
-        <v>0.5194352856</v>
+        <v>0.5184029284</v>
       </c>
       <c r="Q4">
-        <v>0.6274352855999999</v>
+        <v>0.6264029284</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1650641023087622</v>
+        <v>0.16592996627209</v>
       </c>
       <c r="T4">
-        <v>0.8315621022031371</v>
+        <v>0.837599288947751</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>252.5773056070128</v>
+        <v>168.3848704046752</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1620083672839273</v>
+        <v>0.1615497143052675</v>
       </c>
       <c r="C5">
-        <v>2.888078697451431</v>
+        <v>2.868324216000063</v>
       </c>
       <c r="D5">
-        <v>2.414038697451431</v>
+        <v>2.423604216000063</v>
       </c>
       <c r="E5">
-        <v>-0.11404</v>
+        <v>-0.08472000000000002</v>
       </c>
       <c r="F5">
-        <v>0.08796</v>
+        <v>0.11728</v>
       </c>
       <c r="G5">
         <v>0.5620000000000001</v>
@@ -1825,28 +1825,28 @@
         <v>0.745</v>
       </c>
       <c r="M5">
-        <v>0.004424388</v>
+        <v>0.005899183999999999</v>
       </c>
       <c r="N5">
-        <v>0.740575612</v>
+        <v>0.739100816</v>
       </c>
       <c r="O5">
-        <v>0.2221726836</v>
+        <v>0.2217302448</v>
       </c>
       <c r="P5">
-        <v>0.5184029284</v>
+        <v>0.5173705712</v>
       </c>
       <c r="Q5">
-        <v>0.6264029284</v>
+        <v>0.6253705711999999</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.16592996627209</v>
+        <v>0.166813869067987</v>
       </c>
       <c r="T5">
-        <v>0.837599288947751</v>
+        <v>0.8437622504162112</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>168.3848704046752</v>
+        <v>126.2886528035064</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1615497143052675</v>
+        <v>0.1610910613266078</v>
       </c>
       <c r="C6">
-        <v>2.868324216000063</v>
+        <v>2.848645841985375</v>
       </c>
       <c r="D6">
-        <v>2.423604216000063</v>
+        <v>2.433245841985375</v>
       </c>
       <c r="E6">
-        <v>-0.08472000000000002</v>
+        <v>-0.0554</v>
       </c>
       <c r="F6">
-        <v>0.11728</v>
+        <v>0.1466</v>
       </c>
       <c r="G6">
         <v>0.5620000000000001</v>
@@ -1907,28 +1907,28 @@
         <v>0.745</v>
       </c>
       <c r="M6">
-        <v>0.005899183999999999</v>
+        <v>0.00737398</v>
       </c>
       <c r="N6">
-        <v>0.739100816</v>
+        <v>0.73762602</v>
       </c>
       <c r="O6">
-        <v>0.2217302448</v>
+        <v>0.221287806</v>
       </c>
       <c r="P6">
-        <v>0.5173705712</v>
+        <v>0.516338214</v>
       </c>
       <c r="Q6">
-        <v>0.6253705711999999</v>
+        <v>0.624338214</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.166813869067987</v>
+        <v>0.1677163803437977</v>
       </c>
       <c r="T6">
-        <v>0.8437622504162112</v>
+        <v>0.8500549584419022</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>126.2886528035064</v>
+        <v>101.0309222428051</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1610910613266078</v>
+        <v>0.1606324083479481</v>
       </c>
       <c r="C7">
-        <v>2.848645841985375</v>
+        <v>2.829044487351205</v>
       </c>
       <c r="D7">
-        <v>2.433245841985375</v>
+        <v>2.442964487351205</v>
       </c>
       <c r="E7">
-        <v>-0.0554</v>
+        <v>-0.02607999999999999</v>
       </c>
       <c r="F7">
-        <v>0.1466</v>
+        <v>0.17592</v>
       </c>
       <c r="G7">
         <v>0.5620000000000001</v>
@@ -1989,28 +1989,28 @@
         <v>0.745</v>
       </c>
       <c r="M7">
-        <v>0.00737398</v>
+        <v>0.008848776000000001</v>
       </c>
       <c r="N7">
-        <v>0.73762602</v>
+        <v>0.736151224</v>
       </c>
       <c r="O7">
-        <v>0.221287806</v>
+        <v>0.2208453672</v>
       </c>
       <c r="P7">
-        <v>0.516338214</v>
+        <v>0.5153058568</v>
       </c>
       <c r="Q7">
-        <v>0.624338214</v>
+        <v>0.6233058567999999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1677163803437977</v>
+        <v>0.1686380939871789</v>
       </c>
       <c r="T7">
-        <v>0.8500549584419022</v>
+        <v>0.856481553872395</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>101.0309222428051</v>
+        <v>84.19243520233758</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1606324083479481</v>
+        <v>0.1601737553692884</v>
       </c>
       <c r="C8">
-        <v>2.829044487351205</v>
+        <v>2.809521078669429</v>
       </c>
       <c r="D8">
-        <v>2.442964487351205</v>
+        <v>2.452761078669429</v>
       </c>
       <c r="E8">
-        <v>-0.02608000000000002</v>
+        <v>0.003239999999999965</v>
       </c>
       <c r="F8">
-        <v>0.17592</v>
+        <v>0.20524</v>
       </c>
       <c r="G8">
         <v>0.5620000000000001</v>
@@ -2071,28 +2071,28 @@
         <v>0.745</v>
       </c>
       <c r="M8">
-        <v>0.008848775999999999</v>
+        <v>0.010323572</v>
       </c>
       <c r="N8">
-        <v>0.736151224</v>
+        <v>0.734676428</v>
       </c>
       <c r="O8">
-        <v>0.2208453672</v>
+        <v>0.2204029284</v>
       </c>
       <c r="P8">
-        <v>0.5153058568</v>
+        <v>0.5142734996</v>
       </c>
       <c r="Q8">
-        <v>0.6233058567999999</v>
+        <v>0.6222734996</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1686380939871789</v>
+        <v>0.1695796294293424</v>
       </c>
       <c r="T8">
-        <v>0.856481553872395</v>
+        <v>0.8630463556562319</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -2109,7 +2109,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>84.19243520233759</v>
+        <v>72.16494445914653</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1601737553692884</v>
+        <v>0.1597151023906287</v>
       </c>
       <c r="C9">
-        <v>2.809521078669429</v>
+        <v>2.790076557434436</v>
       </c>
       <c r="D9">
-        <v>2.452761078669429</v>
+        <v>2.462636557434437</v>
       </c>
       <c r="E9">
-        <v>0.003239999999999993</v>
+        <v>0.03255999999999998</v>
       </c>
       <c r="F9">
-        <v>0.20524</v>
+        <v>0.23456</v>
       </c>
       <c r="G9">
         <v>0.5620000000000001</v>
@@ -2153,28 +2153,28 @@
         <v>0.745</v>
       </c>
       <c r="M9">
-        <v>0.010323572</v>
+        <v>0.011798368</v>
       </c>
       <c r="N9">
-        <v>0.734676428</v>
+        <v>0.733201632</v>
       </c>
       <c r="O9">
-        <v>0.2204029284</v>
+        <v>0.2199604896</v>
       </c>
       <c r="P9">
-        <v>0.5142734996</v>
+        <v>0.5132411424</v>
       </c>
       <c r="Q9">
-        <v>0.6222734996</v>
+        <v>0.6212411423999999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1695796294293424</v>
+        <v>0.1705416330332921</v>
       </c>
       <c r="T9">
-        <v>0.8630463556562319</v>
+        <v>0.869753870522326</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>72.16494445914651</v>
+        <v>63.1443264017532</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1597151023906287</v>
+        <v>0.159256449411969</v>
       </c>
       <c r="C10">
-        <v>2.790076557434436</v>
+        <v>2.770711880364757</v>
       </c>
       <c r="D10">
-        <v>2.462636557434437</v>
+        <v>2.472591880364757</v>
       </c>
       <c r="E10">
-        <v>0.03255999999999998</v>
+        <v>0.06187999999999999</v>
       </c>
       <c r="F10">
-        <v>0.23456</v>
+        <v>0.26388</v>
       </c>
       <c r="G10">
         <v>0.5620000000000001</v>
@@ -2235,28 +2235,28 @@
         <v>0.745</v>
       </c>
       <c r="M10">
-        <v>0.011798368</v>
+        <v>0.013273164</v>
       </c>
       <c r="N10">
-        <v>0.733201632</v>
+        <v>0.731726836</v>
       </c>
       <c r="O10">
-        <v>0.2199604896</v>
+        <v>0.2195180508</v>
       </c>
       <c r="P10">
-        <v>0.5132411424</v>
+        <v>0.5122087852</v>
       </c>
       <c r="Q10">
-        <v>0.6212411423999999</v>
+        <v>0.6202087852</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1705416330332921</v>
+        <v>0.1715247795735923</v>
       </c>
       <c r="T10">
-        <v>0.869753870522326</v>
+        <v>0.8766088032975649</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>63.1443264017532</v>
+        <v>56.12829013489173</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.159256449411969</v>
+        <v>0.1587977964333092</v>
       </c>
       <c r="C11">
-        <v>2.770711880364757</v>
+        <v>2.751428019712027</v>
       </c>
       <c r="D11">
-        <v>2.472591880364757</v>
+        <v>2.482628019712027</v>
       </c>
       <c r="E11">
-        <v>0.06187999999999999</v>
+        <v>0.09119999999999995</v>
       </c>
       <c r="F11">
-        <v>0.26388</v>
+        <v>0.2932</v>
       </c>
       <c r="G11">
         <v>0.5620000000000001</v>
@@ -2317,28 +2317,28 @@
         <v>0.745</v>
       </c>
       <c r="M11">
-        <v>0.013273164</v>
+        <v>0.01474796</v>
       </c>
       <c r="N11">
-        <v>0.731726836</v>
+        <v>0.73025204</v>
       </c>
       <c r="O11">
-        <v>0.2195180508</v>
+        <v>0.219075612</v>
       </c>
       <c r="P11">
-        <v>0.5122087852</v>
+        <v>0.511176428</v>
       </c>
       <c r="Q11">
-        <v>0.6202087852</v>
+        <v>0.6191764279999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1715247795735923</v>
+        <v>0.172529773814788</v>
       </c>
       <c r="T11">
-        <v>0.8766088032975649</v>
+        <v>0.8836160679122537</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>56.12829013489173</v>
+        <v>50.51546112140256</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1587977964333092</v>
+        <v>0.1583391434546495</v>
       </c>
       <c r="C12">
-        <v>2.751428019712027</v>
+        <v>2.732225963577522</v>
       </c>
       <c r="D12">
-        <v>2.482628019712027</v>
+        <v>2.492745963577522</v>
       </c>
       <c r="E12">
-        <v>0.0912</v>
+        <v>0.12052</v>
       </c>
       <c r="F12">
-        <v>0.2932</v>
+        <v>0.32252</v>
       </c>
       <c r="G12">
         <v>0.5620000000000001</v>
@@ -2399,28 +2399,28 @@
         <v>0.745</v>
       </c>
       <c r="M12">
-        <v>0.01474796</v>
+        <v>0.016222756</v>
       </c>
       <c r="N12">
-        <v>0.73025204</v>
+        <v>0.728777244</v>
       </c>
       <c r="O12">
-        <v>0.219075612</v>
+        <v>0.2186331732</v>
       </c>
       <c r="P12">
-        <v>0.511176428</v>
+        <v>0.5101440708</v>
       </c>
       <c r="Q12">
-        <v>0.6191764279999999</v>
+        <v>0.6181440708</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.172529773814788</v>
+        <v>0.1735573521962354</v>
       </c>
       <c r="T12">
-        <v>0.8836160679122537</v>
+        <v>0.8907807991474972</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2437,7 +2437,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>50.51546112140255</v>
+        <v>45.92314647400233</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1583391434546495</v>
+        <v>0.1578804904759898</v>
       </c>
       <c r="C13">
-        <v>2.732225963577522</v>
+        <v>2.713106716236449</v>
       </c>
       <c r="D13">
-        <v>2.492745963577522</v>
+        <v>2.502946716236448</v>
       </c>
       <c r="E13">
-        <v>0.12052</v>
+        <v>0.14984</v>
       </c>
       <c r="F13">
-        <v>0.32252</v>
+        <v>0.35184</v>
       </c>
       <c r="G13">
         <v>0.5620000000000001</v>
@@ -2481,28 +2481,28 @@
         <v>0.745</v>
       </c>
       <c r="M13">
-        <v>0.016222756</v>
+        <v>0.017697552</v>
       </c>
       <c r="N13">
-        <v>0.728777244</v>
+        <v>0.727302448</v>
       </c>
       <c r="O13">
-        <v>0.2186331732</v>
+        <v>0.2181907344</v>
       </c>
       <c r="P13">
-        <v>0.5101440708</v>
+        <v>0.5091117136</v>
       </c>
       <c r="Q13">
-        <v>0.6181440708</v>
+        <v>0.6171117135999999</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1735573521962354</v>
+        <v>0.1746082846318066</v>
       </c>
       <c r="T13">
-        <v>0.8907807991474972</v>
+        <v>0.8981083651835419</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>45.92314647400233</v>
+        <v>42.0962176011688</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1578804904759898</v>
+        <v>0.1574218374973301</v>
       </c>
       <c r="C14">
-        <v>2.713106716236449</v>
+        <v>2.694071298470243</v>
       </c>
       <c r="D14">
-        <v>2.502946716236448</v>
+        <v>2.513231298470243</v>
       </c>
       <c r="E14">
-        <v>0.14984</v>
+        <v>0.17916</v>
       </c>
       <c r="F14">
-        <v>0.35184</v>
+        <v>0.38116</v>
       </c>
       <c r="G14">
         <v>0.5620000000000001</v>
@@ -2563,28 +2563,28 @@
         <v>0.745</v>
       </c>
       <c r="M14">
-        <v>0.017697552</v>
+        <v>0.019172348</v>
       </c>
       <c r="N14">
-        <v>0.727302448</v>
+        <v>0.725827652</v>
       </c>
       <c r="O14">
-        <v>0.2181907344</v>
+        <v>0.2177482956</v>
       </c>
       <c r="P14">
-        <v>0.5091117136</v>
+        <v>0.5080793564</v>
       </c>
       <c r="Q14">
-        <v>0.6171117135999999</v>
+        <v>0.6160793564</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1746082846318066</v>
+        <v>0.1756833764337127</v>
       </c>
       <c r="T14">
-        <v>0.8981083651835419</v>
+        <v>0.9056043810135184</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>42.0962176011688</v>
+        <v>38.8580470164635</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1574218374973301</v>
+        <v>0.1569631845186704</v>
       </c>
       <c r="C15">
-        <v>2.694071298470243</v>
+        <v>2.67512074790708</v>
       </c>
       <c r="D15">
-        <v>2.513231298470243</v>
+        <v>2.52360074790708</v>
       </c>
       <c r="E15">
-        <v>0.17916</v>
+        <v>0.20848</v>
       </c>
       <c r="F15">
-        <v>0.38116</v>
+        <v>0.41048</v>
       </c>
       <c r="G15">
         <v>0.5620000000000001</v>
@@ -2645,28 +2645,28 @@
         <v>0.745</v>
       </c>
       <c r="M15">
-        <v>0.019172348</v>
+        <v>0.020647144</v>
       </c>
       <c r="N15">
-        <v>0.725827652</v>
+        <v>0.724352856</v>
       </c>
       <c r="O15">
-        <v>0.2177482956</v>
+        <v>0.2173058568</v>
       </c>
       <c r="P15">
-        <v>0.5080793564</v>
+        <v>0.5070469992</v>
       </c>
       <c r="Q15">
-        <v>0.6160793564</v>
+        <v>0.6150469991999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1756833764337127</v>
+        <v>0.1767834703705469</v>
       </c>
       <c r="T15">
-        <v>0.9056043810135184</v>
+        <v>0.9132747227930293</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2683,7 +2683,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>38.8580470164635</v>
+        <v>36.08247222957326</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1569631845186704</v>
+        <v>0.1565045315400106</v>
       </c>
       <c r="C16">
-        <v>2.67512074790708</v>
+        <v>2.656256119370869</v>
       </c>
       <c r="D16">
-        <v>2.52360074790708</v>
+        <v>2.534056119370869</v>
       </c>
       <c r="E16">
-        <v>0.20848</v>
+        <v>0.2378000000000001</v>
       </c>
       <c r="F16">
-        <v>0.41048</v>
+        <v>0.4398000000000001</v>
       </c>
       <c r="G16">
         <v>0.5620000000000001</v>
@@ -2727,28 +2727,28 @@
         <v>0.745</v>
       </c>
       <c r="M16">
-        <v>0.020647144</v>
+        <v>0.02212194</v>
       </c>
       <c r="N16">
-        <v>0.724352856</v>
+        <v>0.72287806</v>
       </c>
       <c r="O16">
-        <v>0.2173058568</v>
+        <v>0.216863418</v>
       </c>
       <c r="P16">
-        <v>0.5070469992</v>
+        <v>0.506014642</v>
       </c>
       <c r="Q16">
-        <v>0.6150469991999999</v>
+        <v>0.614014642</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1767834703705469</v>
+        <v>0.1779094488706008</v>
       </c>
       <c r="T16">
-        <v>0.9132747227930293</v>
+        <v>0.9211255432026465</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>36.08247222957326</v>
+        <v>33.67697408093503</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1565045315400106</v>
+        <v>0.1560458785613509</v>
       </c>
       <c r="C17">
-        <v>2.656256119370869</v>
+        <v>2.637478485238937</v>
       </c>
       <c r="D17">
-        <v>2.534056119370869</v>
+        <v>2.544598485238937</v>
       </c>
       <c r="E17">
-        <v>0.2378</v>
+        <v>0.26712</v>
       </c>
       <c r="F17">
-        <v>0.4398</v>
+        <v>0.46912</v>
       </c>
       <c r="G17">
         <v>0.5620000000000001</v>
@@ -2809,28 +2809,28 @@
         <v>0.745</v>
       </c>
       <c r="M17">
-        <v>0.02212194</v>
+        <v>0.023596736</v>
       </c>
       <c r="N17">
-        <v>0.72287806</v>
+        <v>0.721403264</v>
       </c>
       <c r="O17">
-        <v>0.216863418</v>
+        <v>0.2164209792</v>
       </c>
       <c r="P17">
-        <v>0.506014642</v>
+        <v>0.5049822848</v>
       </c>
       <c r="Q17">
-        <v>0.614014642</v>
+        <v>0.6129822847999999</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1779094488706008</v>
+        <v>0.1790622363825606</v>
       </c>
       <c r="T17">
-        <v>0.9211255432026465</v>
+        <v>0.9291632879077306</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>33.67697408093504</v>
+        <v>31.5721632008766</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1560458785613509</v>
+        <v>0.1555872255826912</v>
       </c>
       <c r="C18">
-        <v>2.637478485238937</v>
+        <v>2.618788935808696</v>
       </c>
       <c r="D18">
-        <v>2.544598485238937</v>
+        <v>2.555228935808696</v>
       </c>
       <c r="E18">
-        <v>0.26712</v>
+        <v>0.29644</v>
       </c>
       <c r="F18">
-        <v>0.46912</v>
+        <v>0.49844</v>
       </c>
       <c r="G18">
         <v>0.5620000000000001</v>
@@ -2891,28 +2891,28 @@
         <v>0.745</v>
       </c>
       <c r="M18">
-        <v>0.023596736</v>
+        <v>0.025071532</v>
       </c>
       <c r="N18">
-        <v>0.721403264</v>
+        <v>0.719928468</v>
       </c>
       <c r="O18">
-        <v>0.2164209792</v>
+        <v>0.2159785404</v>
       </c>
       <c r="P18">
-        <v>0.5049822848</v>
+        <v>0.5039499276</v>
       </c>
       <c r="Q18">
-        <v>0.6129822847999999</v>
+        <v>0.6119499276</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1790622363825606</v>
+        <v>0.1802428019068569</v>
       </c>
       <c r="T18">
-        <v>0.9291632879077306</v>
+        <v>0.9373947132081182</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>31.5721632008766</v>
+        <v>29.7149771302368</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1555872255826912</v>
+        <v>0.1551285726040315</v>
       </c>
       <c r="C19">
-        <v>2.618788935808696</v>
+        <v>2.600188579673533</v>
       </c>
       <c r="D19">
-        <v>2.555228935808696</v>
+        <v>2.565948579673533</v>
       </c>
       <c r="E19">
-        <v>0.29644</v>
+        <v>0.32576</v>
       </c>
       <c r="F19">
-        <v>0.49844</v>
+        <v>0.52776</v>
       </c>
       <c r="G19">
         <v>0.5620000000000001</v>
@@ -2973,28 +2973,28 @@
         <v>0.745</v>
       </c>
       <c r="M19">
-        <v>0.025071532</v>
+        <v>0.026546328</v>
       </c>
       <c r="N19">
-        <v>0.719928468</v>
+        <v>0.718453672</v>
       </c>
       <c r="O19">
-        <v>0.2159785404</v>
+        <v>0.2155361016</v>
       </c>
       <c r="P19">
-        <v>0.5039499276</v>
+        <v>0.5029175704</v>
       </c>
       <c r="Q19">
-        <v>0.6119499276</v>
+        <v>0.6109175703999999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1802428019068569</v>
+        <v>0.1814521617122335</v>
       </c>
       <c r="T19">
-        <v>0.9373947132081182</v>
+        <v>0.9458269049792466</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>29.7149771302368</v>
+        <v>28.06414506744586</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1551285726040315</v>
+        <v>0.1546699196253718</v>
       </c>
       <c r="C20">
-        <v>2.600188579673532</v>
+        <v>2.581678544108196</v>
       </c>
       <c r="D20">
-        <v>2.565948579673532</v>
+        <v>2.576758544108196</v>
       </c>
       <c r="E20">
-        <v>0.32576</v>
+        <v>0.35508</v>
       </c>
       <c r="F20">
-        <v>0.52776</v>
+        <v>0.55708</v>
       </c>
       <c r="G20">
         <v>0.5620000000000001</v>
@@ -3055,28 +3055,28 @@
         <v>0.745</v>
       </c>
       <c r="M20">
-        <v>0.026546328</v>
+        <v>0.028021124</v>
       </c>
       <c r="N20">
-        <v>0.718453672</v>
+        <v>0.716978876</v>
       </c>
       <c r="O20">
-        <v>0.2155361016</v>
+        <v>0.2150936628</v>
       </c>
       <c r="P20">
-        <v>0.5029175704</v>
+        <v>0.5018852132</v>
       </c>
       <c r="Q20">
-        <v>0.6109175703999999</v>
+        <v>0.6098852132</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1814521617122335</v>
+        <v>0.1826913822535454</v>
       </c>
       <c r="T20">
-        <v>0.9458269049792466</v>
+        <v>0.9544672990163289</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>28.06414506744586</v>
+        <v>26.58708480073819</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1546699196253718</v>
+        <v>0.1542112666467121</v>
       </c>
       <c r="C21">
-        <v>2.581678544108196</v>
+        <v>2.563259975463974</v>
       </c>
       <c r="D21">
-        <v>2.576758544108196</v>
+        <v>2.587659975463974</v>
       </c>
       <c r="E21">
-        <v>0.35508</v>
+        <v>0.3844</v>
       </c>
       <c r="F21">
-        <v>0.55708</v>
+        <v>0.5864</v>
       </c>
       <c r="G21">
         <v>0.5620000000000001</v>
@@ -3137,28 +3137,28 @@
         <v>0.745</v>
       </c>
       <c r="M21">
-        <v>0.028021124</v>
+        <v>0.02949592</v>
       </c>
       <c r="N21">
-        <v>0.716978876</v>
+        <v>0.71550408</v>
       </c>
       <c r="O21">
-        <v>0.2150936628</v>
+        <v>0.214651224</v>
       </c>
       <c r="P21">
-        <v>0.5018852132</v>
+        <v>0.500852856</v>
       </c>
       <c r="Q21">
-        <v>0.6098852132</v>
+        <v>0.6088528559999999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1826913822535454</v>
+        <v>0.1839615833083901</v>
       </c>
       <c r="T21">
-        <v>0.9544672990163289</v>
+        <v>0.9633237029043384</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>26.58708480073819</v>
+        <v>25.25773056070128</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1542112666467121</v>
+        <v>0.1537526136680524</v>
       </c>
       <c r="C22">
-        <v>2.563259975463974</v>
+        <v>2.544934039573941</v>
       </c>
       <c r="D22">
-        <v>2.587659975463974</v>
+        <v>2.59865403957394</v>
       </c>
       <c r="E22">
-        <v>0.3844</v>
+        <v>0.41372</v>
       </c>
       <c r="F22">
-        <v>0.5864</v>
+        <v>0.61572</v>
       </c>
       <c r="G22">
         <v>0.5620000000000001</v>
@@ -3219,28 +3219,28 @@
         <v>0.745</v>
       </c>
       <c r="M22">
-        <v>0.02949592</v>
+        <v>0.030970716</v>
       </c>
       <c r="N22">
-        <v>0.71550408</v>
+        <v>0.714029284</v>
       </c>
       <c r="O22">
-        <v>0.214651224</v>
+        <v>0.2142087852</v>
       </c>
       <c r="P22">
-        <v>0.500852856</v>
+        <v>0.4998204988</v>
       </c>
       <c r="Q22">
-        <v>0.6088528559999999</v>
+        <v>0.6078204988</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1839615833083901</v>
+        <v>0.185263941351965</v>
       </c>
       <c r="T22">
-        <v>0.9633237029043384</v>
+        <v>0.9724043195490064</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3257,7 +3257,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>25.25773056070128</v>
+        <v>24.05498148638216</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1537526136680523</v>
+        <v>0.1532939606893926</v>
       </c>
       <c r="C23">
-        <v>2.544934039573942</v>
+        <v>2.52670192216858</v>
       </c>
       <c r="D23">
-        <v>2.598654039573942</v>
+        <v>2.60974192216858</v>
       </c>
       <c r="E23">
-        <v>0.4137199999999999</v>
+        <v>0.4430399999999999</v>
       </c>
       <c r="F23">
-        <v>0.6157199999999999</v>
+        <v>0.6450399999999999</v>
       </c>
       <c r="G23">
         <v>0.5620000000000001</v>
@@ -3301,28 +3301,28 @@
         <v>0.745</v>
       </c>
       <c r="M23">
-        <v>0.030970716</v>
+        <v>0.032445512</v>
       </c>
       <c r="N23">
-        <v>0.714029284</v>
+        <v>0.712554488</v>
       </c>
       <c r="O23">
-        <v>0.2142087852</v>
+        <v>0.2137663464</v>
       </c>
       <c r="P23">
-        <v>0.4998204988</v>
+        <v>0.4987881416</v>
       </c>
       <c r="Q23">
-        <v>0.6078204988</v>
+        <v>0.6067881415999999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.185263941351965</v>
+        <v>0.186599693191529</v>
       </c>
       <c r="T23">
-        <v>0.9724043195490062</v>
+        <v>0.9817177725178964</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>24.05498148638217</v>
+        <v>22.96157323700116</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1532939606893926</v>
+        <v>0.1528353077107329</v>
       </c>
       <c r="C24">
-        <v>2.52670192216858</v>
+        <v>2.50856482930209</v>
       </c>
       <c r="D24">
-        <v>2.60974192216858</v>
+        <v>2.62092482930209</v>
       </c>
       <c r="E24">
-        <v>0.4430399999999999</v>
+        <v>0.4723600000000001</v>
       </c>
       <c r="F24">
-        <v>0.6450399999999999</v>
+        <v>0.6743600000000001</v>
       </c>
       <c r="G24">
         <v>0.5620000000000001</v>
@@ -3383,28 +3383,28 @@
         <v>0.745</v>
       </c>
       <c r="M24">
-        <v>0.032445512</v>
+        <v>0.033920308</v>
       </c>
       <c r="N24">
-        <v>0.712554488</v>
+        <v>0.711079692</v>
       </c>
       <c r="O24">
-        <v>0.2137663464</v>
+        <v>0.2133239076</v>
       </c>
       <c r="P24">
-        <v>0.4987881416</v>
+        <v>0.4977557844</v>
       </c>
       <c r="Q24">
-        <v>0.6067881415999999</v>
+        <v>0.6057557844</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.186599693191529</v>
+        <v>0.1879701398840687</v>
       </c>
       <c r="T24">
-        <v>0.9817177725178964</v>
+        <v>0.9912731333561083</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3421,7 +3421,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>22.96157323700116</v>
+        <v>21.9632439658272</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1528353077107329</v>
+        <v>0.1523766547320732</v>
       </c>
       <c r="C25">
-        <v>2.50856482930209</v>
+        <v>2.490523987789702</v>
       </c>
       <c r="D25">
-        <v>2.62092482930209</v>
+        <v>2.632203987789703</v>
       </c>
       <c r="E25">
-        <v>0.4723600000000001</v>
+        <v>0.5016800000000001</v>
       </c>
       <c r="F25">
-        <v>0.6743600000000001</v>
+        <v>0.7036800000000001</v>
       </c>
       <c r="G25">
         <v>0.5620000000000001</v>
@@ -3465,28 +3465,28 @@
         <v>0.745</v>
       </c>
       <c r="M25">
-        <v>0.033920308</v>
+        <v>0.035395104</v>
       </c>
       <c r="N25">
-        <v>0.711079692</v>
+        <v>0.709604896</v>
       </c>
       <c r="O25">
-        <v>0.2133239076</v>
+        <v>0.2128814688</v>
       </c>
       <c r="P25">
-        <v>0.4977557844</v>
+        <v>0.4967234272</v>
       </c>
       <c r="Q25">
-        <v>0.6057557844</v>
+        <v>0.6047234271999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1879701398840687</v>
+        <v>0.1893766509632542</v>
       </c>
       <c r="T25">
-        <v>0.9912731333561083</v>
+        <v>1.001079951058484</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>21.9632439658272</v>
+        <v>21.04810880058439</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1523766547320732</v>
+        <v>0.1519180017534134</v>
       </c>
       <c r="C26">
-        <v>2.490523987789703</v>
+        <v>2.472580645656339</v>
       </c>
       <c r="D26">
-        <v>2.632203987789703</v>
+        <v>2.64358064565634</v>
       </c>
       <c r="E26">
-        <v>0.5016799999999999</v>
+        <v>0.5309999999999999</v>
       </c>
       <c r="F26">
-        <v>0.70368</v>
+        <v>0.733</v>
       </c>
       <c r="G26">
         <v>0.5620000000000001</v>
@@ -3547,28 +3547,28 @@
         <v>0.745</v>
       </c>
       <c r="M26">
-        <v>0.035395104</v>
+        <v>0.0368699</v>
       </c>
       <c r="N26">
-        <v>0.709604896</v>
+        <v>0.7081301</v>
       </c>
       <c r="O26">
-        <v>0.2128814688</v>
+        <v>0.21243903</v>
       </c>
       <c r="P26">
-        <v>0.4967234272</v>
+        <v>0.49569107</v>
       </c>
       <c r="Q26">
-        <v>0.6047234271999999</v>
+        <v>0.60369107</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1893766509632542</v>
+        <v>0.1908206690045513</v>
       </c>
       <c r="T26">
-        <v>1.001079951058484</v>
+        <v>1.011148283899589</v>
       </c>
       <c r="U26">
         <v>0.0503</v>
@@ -3585,7 +3585,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>21.0481088005844</v>
+        <v>20.20618444856102</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1519180017534134</v>
+        <v>0.1514593487747537</v>
       </c>
       <c r="C27">
-        <v>2.472580645656339</v>
+        <v>2.454736072596953</v>
       </c>
       <c r="D27">
-        <v>2.64358064565634</v>
+        <v>2.655056072596953</v>
       </c>
       <c r="E27">
-        <v>0.5309999999999999</v>
+        <v>0.5603199999999999</v>
       </c>
       <c r="F27">
-        <v>0.733</v>
+        <v>0.76232</v>
       </c>
       <c r="G27">
         <v>0.5620000000000001</v>
@@ -3629,28 +3629,28 @@
         <v>0.745</v>
       </c>
       <c r="M27">
-        <v>0.0368699</v>
+        <v>0.038344696</v>
       </c>
       <c r="N27">
-        <v>0.7081301</v>
+        <v>0.706655304</v>
       </c>
       <c r="O27">
-        <v>0.21243903</v>
+        <v>0.2119965912</v>
       </c>
       <c r="P27">
-        <v>0.49569107</v>
+        <v>0.4946587128</v>
       </c>
       <c r="Q27">
-        <v>0.60369107</v>
+        <v>0.6026587127999999</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1908206690045513</v>
+        <v>0.192303714560478</v>
       </c>
       <c r="T27">
-        <v>1.011148283899589</v>
+        <v>1.021488733844508</v>
       </c>
       <c r="U27">
         <v>0.0503</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>20.20618444856102</v>
+        <v>19.42902350823175</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1514593487747537</v>
+        <v>0.151000695796094</v>
       </c>
       <c r="C28">
-        <v>2.454736072596953</v>
+        <v>2.43699156044891</v>
       </c>
       <c r="D28">
-        <v>2.655056072596953</v>
+        <v>2.66663156044891</v>
       </c>
       <c r="E28">
-        <v>0.5603199999999999</v>
+        <v>0.5896399999999999</v>
       </c>
       <c r="F28">
-        <v>0.76232</v>
+        <v>0.79164</v>
       </c>
       <c r="G28">
         <v>0.5620000000000001</v>
@@ -3711,28 +3711,28 @@
         <v>0.745</v>
       </c>
       <c r="M28">
-        <v>0.038344696</v>
+        <v>0.039819492</v>
       </c>
       <c r="N28">
-        <v>0.706655304</v>
+        <v>0.705180508</v>
       </c>
       <c r="O28">
-        <v>0.2119965912</v>
+        <v>0.2115541524</v>
       </c>
       <c r="P28">
-        <v>0.4946587128</v>
+        <v>0.4936263556</v>
       </c>
       <c r="Q28">
-        <v>0.6026587127999999</v>
+        <v>0.6016263556</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.192303714560478</v>
+        <v>0.1938273915014987</v>
       </c>
       <c r="T28">
-        <v>1.021488733844508</v>
+        <v>1.032112483787919</v>
       </c>
       <c r="U28">
         <v>0.0503</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>19.42902350823175</v>
+        <v>18.70943004496391</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.151000695796094</v>
+        <v>0.1505420428174343</v>
       </c>
       <c r="C29">
-        <v>2.43699156044891</v>
+        <v>2.41934842367679</v>
       </c>
       <c r="D29">
-        <v>2.66663156044891</v>
+        <v>2.67830842367679</v>
       </c>
       <c r="E29">
-        <v>0.5896399999999999</v>
+        <v>0.61896</v>
       </c>
       <c r="F29">
-        <v>0.79164</v>
+        <v>0.82096</v>
       </c>
       <c r="G29">
         <v>0.5620000000000001</v>
@@ -3793,28 +3793,28 @@
         <v>0.745</v>
       </c>
       <c r="M29">
-        <v>0.039819492</v>
+        <v>0.041294288</v>
       </c>
       <c r="N29">
-        <v>0.705180508</v>
+        <v>0.703705712</v>
       </c>
       <c r="O29">
-        <v>0.2115541524</v>
+        <v>0.2111117136</v>
       </c>
       <c r="P29">
-        <v>0.4936263556</v>
+        <v>0.4925939984</v>
       </c>
       <c r="Q29">
-        <v>0.6016263556</v>
+        <v>0.6005939983999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1938273915014987</v>
+        <v>0.1953933928019921</v>
       </c>
       <c r="T29">
-        <v>1.032112483787919</v>
+        <v>1.043031337896423</v>
       </c>
       <c r="U29">
         <v>0.0503</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>18.70943004496391</v>
+        <v>18.04123611478663</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1505420428174343</v>
+        <v>0.1500833898387746</v>
       </c>
       <c r="C30">
-        <v>2.41934842367679</v>
+        <v>2.401807999869968</v>
       </c>
       <c r="D30">
-        <v>2.67830842367679</v>
+        <v>2.690087999869968</v>
       </c>
       <c r="E30">
-        <v>0.61896</v>
+        <v>0.64828</v>
       </c>
       <c r="F30">
-        <v>0.82096</v>
+        <v>0.85028</v>
       </c>
       <c r="G30">
         <v>0.5620000000000001</v>
@@ -3875,28 +3875,28 @@
         <v>0.745</v>
       </c>
       <c r="M30">
-        <v>0.041294288</v>
+        <v>0.042769084</v>
       </c>
       <c r="N30">
-        <v>0.703705712</v>
+        <v>0.702230916</v>
       </c>
       <c r="O30">
-        <v>0.2111117136</v>
+        <v>0.2106692748</v>
       </c>
       <c r="P30">
-        <v>0.4925939984</v>
+        <v>0.4915616412</v>
       </c>
       <c r="Q30">
-        <v>0.6005939983999999</v>
+        <v>0.5995616412</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1953933928019921</v>
+        <v>0.1970035068151755</v>
       </c>
       <c r="T30">
-        <v>1.043031337896423</v>
+        <v>1.054257765360097</v>
       </c>
       <c r="U30">
         <v>0.0503</v>
@@ -3913,7 +3913,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>18.04123611478663</v>
+        <v>17.41912452462157</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1500833898387746</v>
+        <v>0.1496247368601148</v>
       </c>
       <c r="C31">
-        <v>2.401807999869969</v>
+        <v>2.384371650253398</v>
       </c>
       <c r="D31">
-        <v>2.690087999869968</v>
+        <v>2.701971650253398</v>
       </c>
       <c r="E31">
-        <v>0.64828</v>
+        <v>0.6776</v>
       </c>
       <c r="F31">
-        <v>0.8502799999999999</v>
+        <v>0.8795999999999999</v>
       </c>
       <c r="G31">
         <v>0.5620000000000001</v>
@@ -3957,28 +3957,28 @@
         <v>0.745</v>
       </c>
       <c r="M31">
-        <v>0.04276908399999999</v>
+        <v>0.04424387999999999</v>
       </c>
       <c r="N31">
-        <v>0.702230916</v>
+        <v>0.70075612</v>
       </c>
       <c r="O31">
-        <v>0.2106692748</v>
+        <v>0.210226836</v>
       </c>
       <c r="P31">
-        <v>0.4915616412</v>
+        <v>0.490529284</v>
       </c>
       <c r="Q31">
-        <v>0.5995616412</v>
+        <v>0.5985292839999999</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1970035068151755</v>
+        <v>0.1986596240858784</v>
       </c>
       <c r="T31">
-        <v>1.054257765360097</v>
+        <v>1.065804947894162</v>
       </c>
       <c r="U31">
         <v>0.0503</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>17.41912452462157</v>
+        <v>16.83848704046752</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1496247368601148</v>
+        <v>0.1491660838814551</v>
       </c>
       <c r="C32">
-        <v>2.384371650253398</v>
+        <v>2.36704076021198</v>
       </c>
       <c r="D32">
-        <v>2.701971650253398</v>
+        <v>2.71396076021198</v>
       </c>
       <c r="E32">
-        <v>0.6776</v>
+        <v>0.70692</v>
       </c>
       <c r="F32">
-        <v>0.8795999999999999</v>
+        <v>0.90892</v>
       </c>
       <c r="G32">
         <v>0.5620000000000001</v>
@@ -4039,28 +4039,28 @@
         <v>0.745</v>
       </c>
       <c r="M32">
-        <v>0.04424387999999999</v>
+        <v>0.04571867599999999</v>
       </c>
       <c r="N32">
-        <v>0.70075612</v>
+        <v>0.699281324</v>
       </c>
       <c r="O32">
-        <v>0.210226836</v>
+        <v>0.2097843972</v>
       </c>
       <c r="P32">
-        <v>0.490529284</v>
+        <v>0.4894969268</v>
       </c>
       <c r="Q32">
-        <v>0.5985292839999999</v>
+        <v>0.5974969268</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1986596240858784</v>
+        <v>0.2003637447557321</v>
       </c>
       <c r="T32">
-        <v>1.065804947894162</v>
+        <v>1.077686831371242</v>
       </c>
       <c r="U32">
         <v>0.0503</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>16.83848704046752</v>
+        <v>16.29531003916212</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1491660838814551</v>
+        <v>0.1487074309027954</v>
       </c>
       <c r="C33">
-        <v>2.36704076021198</v>
+        <v>2.349816739828968</v>
       </c>
       <c r="D33">
-        <v>2.71396076021198</v>
+        <v>2.726056739828968</v>
       </c>
       <c r="E33">
-        <v>0.70692</v>
+        <v>0.73624</v>
       </c>
       <c r="F33">
-        <v>0.90892</v>
+        <v>0.93824</v>
       </c>
       <c r="G33">
         <v>0.5620000000000001</v>
@@ -4121,28 +4121,28 @@
         <v>0.745</v>
       </c>
       <c r="M33">
-        <v>0.04571867599999999</v>
+        <v>0.04719347199999999</v>
       </c>
       <c r="N33">
-        <v>0.699281324</v>
+        <v>0.697806528</v>
       </c>
       <c r="O33">
-        <v>0.2097843972</v>
+        <v>0.2093419584</v>
       </c>
       <c r="P33">
-        <v>0.4894969268</v>
+        <v>0.4884645696</v>
       </c>
       <c r="Q33">
-        <v>0.5974969268</v>
+        <v>0.5964645695999999</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2003637447557321</v>
+        <v>0.202117986621758</v>
       </c>
       <c r="T33">
-        <v>1.077686831371242</v>
+        <v>1.089918182009414</v>
       </c>
       <c r="U33">
         <v>0.0503</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>16.29531003916212</v>
+        <v>15.7860816004383</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1487074309027954</v>
+        <v>0.1482487779241357</v>
       </c>
       <c r="C34">
-        <v>2.349816739828968</v>
+        <v>2.332701024438824</v>
       </c>
       <c r="D34">
-        <v>2.726056739828968</v>
+        <v>2.738261024438823</v>
       </c>
       <c r="E34">
-        <v>0.73624</v>
+        <v>0.76556</v>
       </c>
       <c r="F34">
-        <v>0.93824</v>
+        <v>0.96756</v>
       </c>
       <c r="G34">
         <v>0.5620000000000001</v>
@@ -4203,28 +4203,28 @@
         <v>0.745</v>
       </c>
       <c r="M34">
-        <v>0.04719347199999999</v>
+        <v>0.04866826799999999</v>
       </c>
       <c r="N34">
-        <v>0.697806528</v>
+        <v>0.696331732</v>
       </c>
       <c r="O34">
-        <v>0.2093419584</v>
+        <v>0.2088995196</v>
       </c>
       <c r="P34">
-        <v>0.4884645696</v>
+        <v>0.4874322124</v>
       </c>
       <c r="Q34">
-        <v>0.5964645695999999</v>
+        <v>0.5954322124</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.202117986621758</v>
+        <v>0.2039245939166205</v>
       </c>
       <c r="T34">
-        <v>1.089918182009414</v>
+        <v>1.102514647592009</v>
       </c>
       <c r="U34">
         <v>0.0503</v>
@@ -4241,7 +4241,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>15.7860816004383</v>
+        <v>15.30771549133411</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1482487779241357</v>
+        <v>0.147790124945476</v>
       </c>
       <c r="C35">
-        <v>2.332701024438824</v>
+        <v>2.315695075194993</v>
       </c>
       <c r="D35">
-        <v>2.738261024438823</v>
+        <v>2.750575075194993</v>
       </c>
       <c r="E35">
-        <v>0.76556</v>
+        <v>0.79488</v>
       </c>
       <c r="F35">
-        <v>0.96756</v>
+        <v>0.9968800000000001</v>
       </c>
       <c r="G35">
         <v>0.5620000000000001</v>
@@ -4285,28 +4285,28 @@
         <v>0.745</v>
       </c>
       <c r="M35">
-        <v>0.04866826799999999</v>
+        <v>0.050143064</v>
       </c>
       <c r="N35">
-        <v>0.696331732</v>
+        <v>0.694856936</v>
       </c>
       <c r="O35">
-        <v>0.2088995196</v>
+        <v>0.2084570808</v>
       </c>
       <c r="P35">
-        <v>0.4874322124</v>
+        <v>0.4863998552</v>
       </c>
       <c r="Q35">
-        <v>0.5954322124</v>
+        <v>0.5943998551999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2039245939166205</v>
+        <v>0.2057859468870848</v>
       </c>
       <c r="T35">
-        <v>1.102514647592009</v>
+        <v>1.115492824252864</v>
       </c>
       <c r="U35">
         <v>0.0503</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>15.30771549133411</v>
+        <v>14.8574885651184</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.147790124945476</v>
+        <v>0.1473314719668163</v>
       </c>
       <c r="C36">
-        <v>2.315695075194993</v>
+        <v>2.298800379653079</v>
       </c>
       <c r="D36">
-        <v>2.750575075194993</v>
+        <v>2.763000379653079</v>
       </c>
       <c r="E36">
-        <v>0.79488</v>
+        <v>0.8242</v>
       </c>
       <c r="F36">
-        <v>0.9968800000000001</v>
+        <v>1.0262</v>
       </c>
       <c r="G36">
         <v>0.5620000000000001</v>
@@ -4367,28 +4367,28 @@
         <v>0.745</v>
       </c>
       <c r="M36">
-        <v>0.050143064</v>
+        <v>0.05161785999999999</v>
       </c>
       <c r="N36">
-        <v>0.694856936</v>
+        <v>0.69338214</v>
       </c>
       <c r="O36">
-        <v>0.2084570808</v>
+        <v>0.208014642</v>
       </c>
       <c r="P36">
-        <v>0.4863998552</v>
+        <v>0.485367498</v>
       </c>
       <c r="Q36">
-        <v>0.5943998551999999</v>
+        <v>0.593367498</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2057859468870848</v>
+        <v>0.2077045722566404</v>
       </c>
       <c r="T36">
-        <v>1.115492824252864</v>
+        <v>1.128870329426361</v>
       </c>
       <c r="U36">
         <v>0.0503</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>14.8574885651184</v>
+        <v>14.4329888918293</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1473314719668163</v>
+        <v>0.1468728189881565</v>
       </c>
       <c r="C37">
-        <v>2.298800379653079</v>
+        <v>2.282018452369882</v>
       </c>
       <c r="D37">
-        <v>2.763000379653079</v>
+        <v>2.775538452369882</v>
       </c>
       <c r="E37">
-        <v>0.8242</v>
+        <v>0.8535200000000001</v>
       </c>
       <c r="F37">
-        <v>1.0262</v>
+        <v>1.05552</v>
       </c>
       <c r="G37">
         <v>0.5620000000000001</v>
@@ -4449,28 +4449,28 @@
         <v>0.745</v>
       </c>
       <c r="M37">
-        <v>0.05161785999999999</v>
+        <v>0.053092656</v>
       </c>
       <c r="N37">
-        <v>0.69338214</v>
+        <v>0.691907344</v>
       </c>
       <c r="O37">
-        <v>0.208014642</v>
+        <v>0.2075722032</v>
       </c>
       <c r="P37">
-        <v>0.485367498</v>
+        <v>0.4843351408</v>
       </c>
       <c r="Q37">
-        <v>0.593367498</v>
+        <v>0.5923351407999999</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2077045722566404</v>
+        <v>0.2096831546689946</v>
       </c>
       <c r="T37">
-        <v>1.128870329426361</v>
+        <v>1.142665881636529</v>
       </c>
       <c r="U37">
         <v>0.0503</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>14.4329888918293</v>
+        <v>14.03207253372293</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1468728189881566</v>
+        <v>0.1464141660094968</v>
       </c>
       <c r="C38">
-        <v>2.282018452369881</v>
+        <v>2.265350835518832</v>
       </c>
       <c r="D38">
-        <v>2.775538452369882</v>
+        <v>2.788190835518831</v>
       </c>
       <c r="E38">
-        <v>0.8535200000000001</v>
+        <v>0.8828400000000001</v>
       </c>
       <c r="F38">
-        <v>1.05552</v>
+        <v>1.08484</v>
       </c>
       <c r="G38">
         <v>0.5620000000000001</v>
@@ -4531,28 +4531,28 @@
         <v>0.745</v>
       </c>
       <c r="M38">
-        <v>0.053092656</v>
+        <v>0.054567452</v>
       </c>
       <c r="N38">
-        <v>0.691907344</v>
+        <v>0.690432548</v>
       </c>
       <c r="O38">
-        <v>0.2075722032</v>
+        <v>0.2071297644</v>
       </c>
       <c r="P38">
-        <v>0.4843351408</v>
+        <v>0.4833027836</v>
       </c>
       <c r="Q38">
-        <v>0.5923351407999999</v>
+        <v>0.5913027836</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2096831546689946</v>
+        <v>0.2117245492214235</v>
       </c>
       <c r="T38">
-        <v>1.142665881636529</v>
+        <v>1.156899387885115</v>
       </c>
       <c r="U38">
         <v>0.0503</v>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>14.03207253372293</v>
+        <v>13.6528273301088</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1464141660094968</v>
+        <v>0.1459555130308371</v>
       </c>
       <c r="C39">
-        <v>2.265350835518832</v>
+        <v>2.248799099522318</v>
       </c>
       <c r="D39">
-        <v>2.788190835518831</v>
+        <v>2.800959099522318</v>
       </c>
       <c r="E39">
-        <v>0.8828400000000001</v>
+        <v>0.9121600000000001</v>
       </c>
       <c r="F39">
-        <v>1.08484</v>
+        <v>1.11416</v>
       </c>
       <c r="G39">
         <v>0.5620000000000001</v>
@@ -4613,28 +4613,28 @@
         <v>0.745</v>
       </c>
       <c r="M39">
-        <v>0.054567452</v>
+        <v>0.056042248</v>
       </c>
       <c r="N39">
-        <v>0.690432548</v>
+        <v>0.688957752</v>
       </c>
       <c r="O39">
-        <v>0.2071297644</v>
+        <v>0.2066873256</v>
       </c>
       <c r="P39">
-        <v>0.4833027836</v>
+        <v>0.4822704264</v>
       </c>
       <c r="Q39">
-        <v>0.5913027836</v>
+        <v>0.5902704263999999</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2117245492214235</v>
+        <v>0.2138317952110276</v>
       </c>
       <c r="T39">
-        <v>1.156899387885115</v>
+        <v>1.17159203949656</v>
       </c>
       <c r="U39">
         <v>0.0503</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>13.6528273301088</v>
+        <v>13.29354240036909</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1459555130308371</v>
+        <v>0.1454968600521774</v>
       </c>
       <c r="C40">
-        <v>2.248799099522318</v>
+        <v>2.232364843701499</v>
       </c>
       <c r="D40">
-        <v>2.800959099522318</v>
+        <v>2.813844843701499</v>
       </c>
       <c r="E40">
-        <v>0.9121600000000001</v>
+        <v>0.9414800000000001</v>
       </c>
       <c r="F40">
-        <v>1.11416</v>
+        <v>1.14348</v>
       </c>
       <c r="G40">
         <v>0.5620000000000001</v>
@@ -4695,28 +4695,28 @@
         <v>0.745</v>
       </c>
       <c r="M40">
-        <v>0.056042248</v>
+        <v>0.057517044</v>
       </c>
       <c r="N40">
-        <v>0.688957752</v>
+        <v>0.687482956</v>
       </c>
       <c r="O40">
-        <v>0.2066873256</v>
+        <v>0.2062448868</v>
       </c>
       <c r="P40">
-        <v>0.4822704264</v>
+        <v>0.4812380692</v>
       </c>
       <c r="Q40">
-        <v>0.5902704263999999</v>
+        <v>0.5892380692</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2138317952110276</v>
+        <v>0.2160081312330777</v>
       </c>
       <c r="T40">
-        <v>1.17159203949656</v>
+        <v>1.186766417390346</v>
       </c>
       <c r="U40">
         <v>0.0503</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>13.29354240036909</v>
+        <v>12.95268233882117</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1454968600521774</v>
+        <v>0.1454582070735177</v>
       </c>
       <c r="C41">
-        <v>2.232364843701499</v>
+        <v>2.204136208757014</v>
       </c>
       <c r="D41">
-        <v>2.813844843701499</v>
+        <v>2.814936208757014</v>
       </c>
       <c r="E41">
-        <v>0.9414800000000001</v>
+        <v>0.9708000000000001</v>
       </c>
       <c r="F41">
-        <v>1.14348</v>
+        <v>1.1728</v>
       </c>
       <c r="G41">
         <v>0.5620000000000001</v>
@@ -4777,45 +4777,45 @@
         <v>0.745</v>
       </c>
       <c r="M41">
-        <v>0.057517044</v>
+        <v>0.06075104</v>
       </c>
       <c r="N41">
-        <v>0.687482956</v>
+        <v>0.68424896</v>
       </c>
       <c r="O41">
-        <v>0.2062448868</v>
+        <v>0.205274688</v>
       </c>
       <c r="P41">
-        <v>0.4812380692</v>
+        <v>0.478974272</v>
       </c>
       <c r="Q41">
-        <v>0.5892380692</v>
+        <v>0.586974272</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2160081312330777</v>
+        <v>0.2182570117891961</v>
       </c>
       <c r="T41">
-        <v>1.186766417390346</v>
+        <v>1.202446607880593</v>
       </c>
       <c r="U41">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V41">
         <v>0.3</v>
       </c>
       <c r="W41">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y41">
-        <v>12.95268233882117</v>
+        <v>12.26316454829415</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1454582070735177</v>
+        <v>0.145010054094858</v>
       </c>
       <c r="C42">
-        <v>2.204136208757014</v>
+        <v>2.187531876117556</v>
       </c>
       <c r="D42">
-        <v>2.814936208757014</v>
+        <v>2.827651876117556</v>
       </c>
       <c r="E42">
-        <v>0.9708000000000001</v>
+        <v>1.00012</v>
       </c>
       <c r="F42">
-        <v>1.1728</v>
+        <v>1.20212</v>
       </c>
       <c r="G42">
         <v>0.5620000000000001</v>
@@ -4859,28 +4859,28 @@
         <v>0.745</v>
       </c>
       <c r="M42">
-        <v>0.06075104</v>
+        <v>0.06226981600000001</v>
       </c>
       <c r="N42">
-        <v>0.68424896</v>
+        <v>0.682730184</v>
       </c>
       <c r="O42">
-        <v>0.205274688</v>
+        <v>0.2048190552</v>
       </c>
       <c r="P42">
-        <v>0.478974272</v>
+        <v>0.4779111288</v>
       </c>
       <c r="Q42">
-        <v>0.586974272</v>
+        <v>0.5859111288</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2182570117891961</v>
+        <v>0.220582125584505</v>
       </c>
       <c r="T42">
-        <v>1.202446607880593</v>
+        <v>1.218658330251864</v>
       </c>
       <c r="U42">
         <v>0.0518</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>12.26316454829415</v>
+        <v>11.96406297394551</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.145010054094858</v>
+        <v>0.1445619011161982</v>
       </c>
       <c r="C43">
-        <v>2.187531876117556</v>
+        <v>2.171042943528904</v>
       </c>
       <c r="D43">
-        <v>2.827651876117556</v>
+        <v>2.840482943528904</v>
       </c>
       <c r="E43">
-        <v>1.00012</v>
+        <v>1.02944</v>
       </c>
       <c r="F43">
-        <v>1.20212</v>
+        <v>1.23144</v>
       </c>
       <c r="G43">
         <v>0.5620000000000001</v>
@@ -4941,28 +4941,28 @@
         <v>0.745</v>
       </c>
       <c r="M43">
-        <v>0.06226981600000001</v>
+        <v>0.06378859200000001</v>
       </c>
       <c r="N43">
-        <v>0.682730184</v>
+        <v>0.681211408</v>
       </c>
       <c r="O43">
-        <v>0.2048190552</v>
+        <v>0.2043634224</v>
       </c>
       <c r="P43">
-        <v>0.4779111288</v>
+        <v>0.4768479856</v>
       </c>
       <c r="Q43">
-        <v>0.5859111288</v>
+        <v>0.5848479856000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.220582125584505</v>
+        <v>0.2229874157175832</v>
       </c>
       <c r="T43">
-        <v>1.218658330251864</v>
+        <v>1.23542907753249</v>
       </c>
       <c r="U43">
         <v>0.0518</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>11.96406297394551</v>
+        <v>11.67920433170872</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1445619011161982</v>
+        <v>0.1441137481375385</v>
       </c>
       <c r="C44">
-        <v>2.171042943528904</v>
+        <v>2.154670989108387</v>
       </c>
       <c r="D44">
-        <v>2.840482943528904</v>
+        <v>2.853430989108387</v>
       </c>
       <c r="E44">
-        <v>1.02944</v>
+        <v>1.05876</v>
       </c>
       <c r="F44">
-        <v>1.23144</v>
+        <v>1.26076</v>
       </c>
       <c r="G44">
         <v>0.5620000000000001</v>
@@ -5023,28 +5023,28 @@
         <v>0.745</v>
       </c>
       <c r="M44">
-        <v>0.06378859199999999</v>
+        <v>0.06530736799999999</v>
       </c>
       <c r="N44">
-        <v>0.681211408</v>
+        <v>0.679692632</v>
       </c>
       <c r="O44">
-        <v>0.2043634224</v>
+        <v>0.2039077896</v>
       </c>
       <c r="P44">
-        <v>0.4768479856</v>
+        <v>0.4757848424</v>
       </c>
       <c r="Q44">
-        <v>0.5848479856000001</v>
+        <v>0.5837848423999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2229874157175831</v>
+        <v>0.2254771019956816</v>
       </c>
       <c r="T44">
-        <v>1.23542907753249</v>
+        <v>1.25278827208612</v>
       </c>
       <c r="U44">
         <v>0.0518</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>11.67920433170872</v>
+        <v>11.40759492864573</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1441137481375385</v>
+        <v>0.1436655951588788</v>
       </c>
       <c r="C45">
-        <v>2.154670989108387</v>
+        <v>2.138417619879832</v>
       </c>
       <c r="D45">
-        <v>2.853430989108387</v>
+        <v>2.866497619879832</v>
       </c>
       <c r="E45">
-        <v>1.05876</v>
+        <v>1.08808</v>
       </c>
       <c r="F45">
-        <v>1.26076</v>
+        <v>1.29008</v>
       </c>
       <c r="G45">
         <v>0.5620000000000001</v>
@@ -5105,28 +5105,28 @@
         <v>0.745</v>
       </c>
       <c r="M45">
-        <v>0.06530736799999999</v>
+        <v>0.06682614399999999</v>
       </c>
       <c r="N45">
-        <v>0.679692632</v>
+        <v>0.678173856</v>
       </c>
       <c r="O45">
-        <v>0.2039077896</v>
+        <v>0.2034521568</v>
       </c>
       <c r="P45">
-        <v>0.4757848424</v>
+        <v>0.4747216992</v>
       </c>
       <c r="Q45">
-        <v>0.5837848423999999</v>
+        <v>0.5827216992000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2254771019956816</v>
+        <v>0.228055705640855</v>
       </c>
       <c r="T45">
-        <v>1.25278827208612</v>
+        <v>1.270767437873808</v>
       </c>
       <c r="U45">
         <v>0.0518</v>
@@ -5143,7 +5143,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>11.40759492864573</v>
+        <v>11.14833140754014</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1436655951588788</v>
+        <v>0.1432174421802191</v>
       </c>
       <c r="C46">
-        <v>2.138417619879832</v>
+        <v>2.122284472438469</v>
       </c>
       <c r="D46">
-        <v>2.866497619879832</v>
+        <v>2.879684472438469</v>
       </c>
       <c r="E46">
-        <v>1.08808</v>
+        <v>1.1174</v>
       </c>
       <c r="F46">
-        <v>1.29008</v>
+        <v>1.3194</v>
       </c>
       <c r="G46">
         <v>0.5620000000000001</v>
@@ -5187,28 +5187,28 @@
         <v>0.745</v>
       </c>
       <c r="M46">
-        <v>0.06682614399999999</v>
+        <v>0.06834491999999999</v>
       </c>
       <c r="N46">
-        <v>0.678173856</v>
+        <v>0.67665508</v>
       </c>
       <c r="O46">
-        <v>0.2034521568</v>
+        <v>0.202996524</v>
       </c>
       <c r="P46">
-        <v>0.4747216992</v>
+        <v>0.473658556</v>
       </c>
       <c r="Q46">
-        <v>0.5827216992000001</v>
+        <v>0.5816585559999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.228055705640855</v>
+        <v>0.2307280766913074</v>
       </c>
       <c r="T46">
-        <v>1.270767437873808</v>
+        <v>1.289400391508321</v>
       </c>
       <c r="U46">
         <v>0.0518</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>11.14833140754014</v>
+        <v>10.9005907095948</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1432174421802191</v>
+        <v>0.1427692892015593</v>
       </c>
       <c r="C47">
-        <v>2.122284472438469</v>
+        <v>2.106273213634262</v>
       </c>
       <c r="D47">
-        <v>2.879684472438469</v>
+        <v>2.892993213634262</v>
       </c>
       <c r="E47">
-        <v>1.1174</v>
+        <v>1.14672</v>
       </c>
       <c r="F47">
-        <v>1.3194</v>
+        <v>1.34872</v>
       </c>
       <c r="G47">
         <v>0.5620000000000001</v>
@@ -5269,28 +5269,28 @@
         <v>0.745</v>
       </c>
       <c r="M47">
-        <v>0.06834491999999999</v>
+        <v>0.069863696</v>
       </c>
       <c r="N47">
-        <v>0.67665508</v>
+        <v>0.675136304</v>
       </c>
       <c r="O47">
-        <v>0.202996524</v>
+        <v>0.2025408912</v>
       </c>
       <c r="P47">
-        <v>0.473658556</v>
+        <v>0.4725954128000001</v>
       </c>
       <c r="Q47">
-        <v>0.5816585559999999</v>
+        <v>0.5805954128</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2307280766913074</v>
+        <v>0.2334994244473321</v>
       </c>
       <c r="T47">
-        <v>1.289400391508321</v>
+        <v>1.308723454536705</v>
       </c>
       <c r="U47">
         <v>0.0518</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>10.9005907095948</v>
+        <v>10.66362134634274</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1427692892015593</v>
+        <v>0.1423211362228996</v>
       </c>
       <c r="C48">
-        <v>2.106273213634262</v>
+        <v>2.090385541274276</v>
       </c>
       <c r="D48">
-        <v>2.892993213634262</v>
+        <v>2.906425541274277</v>
       </c>
       <c r="E48">
-        <v>1.14672</v>
+        <v>1.17604</v>
       </c>
       <c r="F48">
-        <v>1.34872</v>
+        <v>1.37804</v>
       </c>
       <c r="G48">
         <v>0.5620000000000001</v>
@@ -5351,28 +5351,28 @@
         <v>0.745</v>
       </c>
       <c r="M48">
-        <v>0.069863696</v>
+        <v>0.071382472</v>
       </c>
       <c r="N48">
-        <v>0.675136304</v>
+        <v>0.673617528</v>
       </c>
       <c r="O48">
-        <v>0.2025408912</v>
+        <v>0.2020852584</v>
       </c>
       <c r="P48">
-        <v>0.4725954128000001</v>
+        <v>0.4715322695999999</v>
       </c>
       <c r="Q48">
-        <v>0.5805954128</v>
+        <v>0.5795322695999999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2334994244473321</v>
+        <v>0.2363753513639616</v>
       </c>
       <c r="T48">
-        <v>1.308723454536705</v>
+        <v>1.32877568975484</v>
       </c>
       <c r="U48">
         <v>0.0518</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>10.66362134634274</v>
+        <v>10.43673578578226</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1423211362228996</v>
+        <v>0.1418729832442399</v>
       </c>
       <c r="C49">
-        <v>2.090385541274276</v>
+        <v>2.074623184844722</v>
       </c>
       <c r="D49">
-        <v>2.906425541274277</v>
+        <v>2.919983184844722</v>
       </c>
       <c r="E49">
-        <v>1.17604</v>
+        <v>1.20536</v>
       </c>
       <c r="F49">
-        <v>1.37804</v>
+        <v>1.40736</v>
       </c>
       <c r="G49">
         <v>0.5620000000000001</v>
@@ -5433,28 +5433,28 @@
         <v>0.745</v>
       </c>
       <c r="M49">
-        <v>0.071382472</v>
+        <v>0.072901248</v>
       </c>
       <c r="N49">
-        <v>0.673617528</v>
+        <v>0.672098752</v>
       </c>
       <c r="O49">
-        <v>0.2020852584</v>
+        <v>0.2016296256</v>
       </c>
       <c r="P49">
-        <v>0.4715322695999999</v>
+        <v>0.4704691264</v>
       </c>
       <c r="Q49">
-        <v>0.5795322695999999</v>
+        <v>0.5784691264</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2363753513639616</v>
+        <v>0.2393618908543075</v>
       </c>
       <c r="T49">
-        <v>1.32877568975484</v>
+        <v>1.349599164789057</v>
       </c>
       <c r="U49">
         <v>0.0518</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>10.43673578578226</v>
+        <v>10.21930379024513</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1418729832442399</v>
+        <v>0.1414248302655802</v>
       </c>
       <c r="C50">
-        <v>2.074623184844723</v>
+        <v>2.058987906253274</v>
       </c>
       <c r="D50">
-        <v>2.919983184844723</v>
+        <v>2.933667906253274</v>
       </c>
       <c r="E50">
-        <v>1.20536</v>
+        <v>1.23468</v>
       </c>
       <c r="F50">
-        <v>1.40736</v>
+        <v>1.43668</v>
       </c>
       <c r="G50">
         <v>0.5620000000000001</v>
@@ -5515,28 +5515,28 @@
         <v>0.745</v>
       </c>
       <c r="M50">
-        <v>0.072901248</v>
+        <v>0.074420024</v>
       </c>
       <c r="N50">
-        <v>0.672098752</v>
+        <v>0.670579976</v>
       </c>
       <c r="O50">
-        <v>0.2016296256</v>
+        <v>0.2011739928</v>
       </c>
       <c r="P50">
-        <v>0.4704691264</v>
+        <v>0.4694059832</v>
       </c>
       <c r="Q50">
-        <v>0.5784691264</v>
+        <v>0.5774059832</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2393618908543075</v>
+        <v>0.2424655495403533</v>
       </c>
       <c r="T50">
-        <v>1.349599164789057</v>
+        <v>1.37123924668736</v>
       </c>
       <c r="U50">
         <v>0.0518</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>10.21930379024513</v>
+        <v>10.01074657003604</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1414248302655802</v>
+        <v>0.1415716772869205</v>
       </c>
       <c r="C51">
-        <v>2.058987906253274</v>
+        <v>2.025169703800954</v>
       </c>
       <c r="D51">
-        <v>2.933667906253274</v>
+        <v>2.929169703800953</v>
       </c>
       <c r="E51">
-        <v>1.23468</v>
+        <v>1.264</v>
       </c>
       <c r="F51">
-        <v>1.43668</v>
+        <v>1.466</v>
       </c>
       <c r="G51">
         <v>0.5620000000000001</v>
@@ -5597,45 +5597,45 @@
         <v>0.745</v>
       </c>
       <c r="M51">
-        <v>0.074420024</v>
+        <v>0.078431</v>
       </c>
       <c r="N51">
-        <v>0.670579976</v>
+        <v>0.666569</v>
       </c>
       <c r="O51">
-        <v>0.2011739928</v>
+        <v>0.1999707</v>
       </c>
       <c r="P51">
-        <v>0.4694059832</v>
+        <v>0.4665983</v>
       </c>
       <c r="Q51">
-        <v>0.5774059832</v>
+        <v>0.5745983</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2424655495403533</v>
+        <v>0.2456933545738409</v>
       </c>
       <c r="T51">
-        <v>1.37123924668736</v>
+        <v>1.393744931861596</v>
       </c>
       <c r="U51">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V51">
         <v>0.3</v>
       </c>
       <c r="W51">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y51">
-        <v>10.01074657003604</v>
+        <v>9.498795119276815</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1415716772869205</v>
+        <v>0.1411354243082608</v>
       </c>
       <c r="C52">
-        <v>2.025169703800954</v>
+        <v>2.009253525282368</v>
       </c>
       <c r="D52">
-        <v>2.929169703800953</v>
+        <v>2.942573525282369</v>
       </c>
       <c r="E52">
-        <v>1.264</v>
+        <v>1.29332</v>
       </c>
       <c r="F52">
-        <v>1.466</v>
+        <v>1.49532</v>
       </c>
       <c r="G52">
         <v>0.5620000000000001</v>
@@ -5679,28 +5679,28 @@
         <v>0.745</v>
       </c>
       <c r="M52">
-        <v>0.078431</v>
+        <v>0.07999961999999999</v>
       </c>
       <c r="N52">
-        <v>0.666569</v>
+        <v>0.6650003799999999</v>
       </c>
       <c r="O52">
-        <v>0.1999707</v>
+        <v>0.199500114</v>
       </c>
       <c r="P52">
-        <v>0.4665983</v>
+        <v>0.4655002659999999</v>
       </c>
       <c r="Q52">
-        <v>0.5745983</v>
+        <v>0.5735002659999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2456933545738409</v>
+        <v>0.2490529067515526</v>
       </c>
       <c r="T52">
-        <v>1.393744931861596</v>
+        <v>1.417169216430699</v>
       </c>
       <c r="U52">
         <v>0.0535</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>9.498795119276815</v>
+        <v>9.312544234585115</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1411354243082608</v>
+        <v>0.140699171329601</v>
       </c>
       <c r="C53">
-        <v>2.009253525282368</v>
+        <v>1.99346058191884</v>
       </c>
       <c r="D53">
-        <v>2.942573525282369</v>
+        <v>2.95610058191884</v>
       </c>
       <c r="E53">
-        <v>1.29332</v>
+        <v>1.32264</v>
       </c>
       <c r="F53">
-        <v>1.49532</v>
+        <v>1.52464</v>
       </c>
       <c r="G53">
         <v>0.5620000000000001</v>
@@ -5761,28 +5761,28 @@
         <v>0.745</v>
       </c>
       <c r="M53">
-        <v>0.07999961999999999</v>
+        <v>0.08156824</v>
       </c>
       <c r="N53">
-        <v>0.6650003799999999</v>
+        <v>0.66343176</v>
       </c>
       <c r="O53">
-        <v>0.199500114</v>
+        <v>0.199029528</v>
       </c>
       <c r="P53">
-        <v>0.4655002659999999</v>
+        <v>0.464402232</v>
       </c>
       <c r="Q53">
-        <v>0.5735002659999999</v>
+        <v>0.5724022320000001</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2490529067515526</v>
+        <v>0.2525524402700021</v>
       </c>
       <c r="T53">
-        <v>1.417169216430699</v>
+        <v>1.441569512856847</v>
       </c>
       <c r="U53">
         <v>0.0535</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>9.312544234585115</v>
+        <v>9.133456845458477</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.140699171329601</v>
+        <v>0.1402629183509413</v>
       </c>
       <c r="C54">
-        <v>1.99346058191884</v>
+        <v>1.977792581101088</v>
       </c>
       <c r="D54">
-        <v>2.95610058191884</v>
+        <v>2.969752581101088</v>
       </c>
       <c r="E54">
-        <v>1.32264</v>
+        <v>1.35196</v>
       </c>
       <c r="F54">
-        <v>1.52464</v>
+        <v>1.55396</v>
       </c>
       <c r="G54">
         <v>0.5620000000000001</v>
@@ -5843,28 +5843,28 @@
         <v>0.745</v>
       </c>
       <c r="M54">
-        <v>0.08156824</v>
+        <v>0.08313685999999999</v>
       </c>
       <c r="N54">
-        <v>0.66343176</v>
+        <v>0.66186314</v>
       </c>
       <c r="O54">
-        <v>0.199029528</v>
+        <v>0.198558942</v>
       </c>
       <c r="P54">
-        <v>0.464402232</v>
+        <v>0.463304198</v>
       </c>
       <c r="Q54">
-        <v>0.5724022320000001</v>
+        <v>0.571304198</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2525524402700021</v>
+        <v>0.2562008901083858</v>
       </c>
       <c r="T54">
-        <v>1.441569512856847</v>
+        <v>1.467008119769214</v>
       </c>
       <c r="U54">
         <v>0.0535</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>9.133456845458477</v>
+        <v>8.961127471015866</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1402629183509413</v>
+        <v>0.1398266653722816</v>
       </c>
       <c r="C55">
-        <v>1.977792581101088</v>
+        <v>1.962251261906775</v>
       </c>
       <c r="D55">
-        <v>2.969752581101088</v>
+        <v>2.983531261906775</v>
       </c>
       <c r="E55">
-        <v>1.35196</v>
+        <v>1.38128</v>
       </c>
       <c r="F55">
-        <v>1.55396</v>
+        <v>1.58328</v>
       </c>
       <c r="G55">
         <v>0.5620000000000001</v>
@@ -5925,28 +5925,28 @@
         <v>0.745</v>
       </c>
       <c r="M55">
-        <v>0.08313685999999999</v>
+        <v>0.08470548</v>
       </c>
       <c r="N55">
-        <v>0.66186314</v>
+        <v>0.66029452</v>
       </c>
       <c r="O55">
-        <v>0.198558942</v>
+        <v>0.198088356</v>
       </c>
       <c r="P55">
-        <v>0.463304198</v>
+        <v>0.462206164</v>
       </c>
       <c r="Q55">
-        <v>0.571304198</v>
+        <v>0.570206164</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.2562008901083858</v>
+        <v>0.2600079682006122</v>
       </c>
       <c r="T55">
-        <v>1.467008119769214</v>
+        <v>1.493552753069076</v>
       </c>
       <c r="U55">
         <v>0.0535</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>8.961127471015866</v>
+        <v>8.795180665997052</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1398266653722816</v>
+        <v>0.1393904123936219</v>
       </c>
       <c r="C56">
-        <v>1.962251261906775</v>
+        <v>1.94683839583901</v>
       </c>
       <c r="D56">
-        <v>2.983531261906775</v>
+        <v>2.997438395839009</v>
       </c>
       <c r="E56">
-        <v>1.38128</v>
+        <v>1.4106</v>
       </c>
       <c r="F56">
-        <v>1.58328</v>
+        <v>1.6126</v>
       </c>
       <c r="G56">
         <v>0.5620000000000001</v>
@@ -6007,28 +6007,28 @@
         <v>0.745</v>
       </c>
       <c r="M56">
-        <v>0.08470548</v>
+        <v>0.08627410000000001</v>
       </c>
       <c r="N56">
-        <v>0.66029452</v>
+        <v>0.6587259</v>
       </c>
       <c r="O56">
-        <v>0.198088356</v>
+        <v>0.19761777</v>
       </c>
       <c r="P56">
-        <v>0.462206164</v>
+        <v>0.4611081299999999</v>
       </c>
       <c r="Q56">
-        <v>0.570206164</v>
+        <v>0.5691081299999999</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2600079682006122</v>
+        <v>0.2639842497636042</v>
       </c>
       <c r="T56">
-        <v>1.493552753069076</v>
+        <v>1.521277147848932</v>
       </c>
       <c r="U56">
         <v>0.0535</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>8.795180665997052</v>
+        <v>8.63526829025165</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1393904123936219</v>
+        <v>0.1389541594149621</v>
       </c>
       <c r="C57">
-        <v>1.94683839583901</v>
+        <v>1.931555787585618</v>
       </c>
       <c r="D57">
-        <v>2.997438395839009</v>
+        <v>3.011475787585618</v>
       </c>
       <c r="E57">
-        <v>1.4106</v>
+        <v>1.43992</v>
       </c>
       <c r="F57">
-        <v>1.6126</v>
+        <v>1.64192</v>
       </c>
       <c r="G57">
         <v>0.5620000000000001</v>
@@ -6089,28 +6089,28 @@
         <v>0.745</v>
       </c>
       <c r="M57">
-        <v>0.08627410000000001</v>
+        <v>0.08784272</v>
       </c>
       <c r="N57">
-        <v>0.6587259</v>
+        <v>0.65715728</v>
       </c>
       <c r="O57">
-        <v>0.19761777</v>
+        <v>0.197147184</v>
       </c>
       <c r="P57">
-        <v>0.4611081299999999</v>
+        <v>0.460010096</v>
       </c>
       <c r="Q57">
-        <v>0.5691081299999999</v>
+        <v>0.568010096</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.2639842497636042</v>
+        <v>0.2681412713976413</v>
       </c>
       <c r="T57">
-        <v>1.521277147848932</v>
+        <v>1.550261742391508</v>
       </c>
       <c r="U57">
         <v>0.0535</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>8.63526829025165</v>
+        <v>8.481067070782871</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1389541594149621</v>
+        <v>0.1385179064363024</v>
       </c>
       <c r="C58">
-        <v>1.931555787585618</v>
+        <v>1.916405275799833</v>
       </c>
       <c r="D58">
-        <v>3.011475787585618</v>
+        <v>3.025645275799833</v>
       </c>
       <c r="E58">
-        <v>1.43992</v>
+        <v>1.46924</v>
       </c>
       <c r="F58">
-        <v>1.64192</v>
+        <v>1.67124</v>
       </c>
       <c r="G58">
         <v>0.5620000000000001</v>
@@ -6171,28 +6171,28 @@
         <v>0.745</v>
       </c>
       <c r="M58">
-        <v>0.08784272</v>
+        <v>0.08941134000000001</v>
       </c>
       <c r="N58">
-        <v>0.65715728</v>
+        <v>0.65558866</v>
       </c>
       <c r="O58">
-        <v>0.197147184</v>
+        <v>0.196676598</v>
       </c>
       <c r="P58">
-        <v>0.460010096</v>
+        <v>0.458912062</v>
       </c>
       <c r="Q58">
-        <v>0.568010096</v>
+        <v>0.566912062</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2681412713976413</v>
+        <v>0.272491642875122</v>
       </c>
       <c r="T58">
-        <v>1.550261742391508</v>
+        <v>1.580594457610483</v>
       </c>
       <c r="U58">
         <v>0.0535</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>8.481067070782871</v>
+        <v>8.33227642041826</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1385179064363024</v>
+        <v>0.1380816534576427</v>
       </c>
       <c r="C59">
-        <v>1.916405275799833</v>
+        <v>1.90138873390314</v>
       </c>
       <c r="D59">
-        <v>3.025645275799833</v>
+        <v>3.03994873390314</v>
       </c>
       <c r="E59">
-        <v>1.46924</v>
+        <v>1.49856</v>
       </c>
       <c r="F59">
-        <v>1.67124</v>
+        <v>1.70056</v>
       </c>
       <c r="G59">
         <v>0.5620000000000001</v>
@@ -6253,28 +6253,28 @@
         <v>0.745</v>
       </c>
       <c r="M59">
-        <v>0.08941134000000001</v>
+        <v>0.09097996</v>
       </c>
       <c r="N59">
-        <v>0.65558866</v>
+        <v>0.65402004</v>
       </c>
       <c r="O59">
-        <v>0.196676598</v>
+        <v>0.196206012</v>
       </c>
       <c r="P59">
-        <v>0.458912062</v>
+        <v>0.457814028</v>
       </c>
       <c r="Q59">
-        <v>0.566912062</v>
+        <v>0.565814028</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.272491642875122</v>
+        <v>0.2770491748991493</v>
       </c>
       <c r="T59">
-        <v>1.580594457610483</v>
+        <v>1.612371587839886</v>
       </c>
       <c r="U59">
         <v>0.0535</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>8.33227642041826</v>
+        <v>8.188616482135188</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1380816534576427</v>
+        <v>0.137645400478983</v>
       </c>
       <c r="C60">
-        <v>1.90138873390314</v>
+        <v>1.886508070911003</v>
       </c>
       <c r="D60">
-        <v>3.03994873390314</v>
+        <v>3.054388070911003</v>
       </c>
       <c r="E60">
-        <v>1.49856</v>
+        <v>1.52788</v>
       </c>
       <c r="F60">
-        <v>1.70056</v>
+        <v>1.72988</v>
       </c>
       <c r="G60">
         <v>0.5620000000000001</v>
@@ -6335,28 +6335,28 @@
         <v>0.745</v>
       </c>
       <c r="M60">
-        <v>0.09097995999999998</v>
+        <v>0.09254857999999999</v>
       </c>
       <c r="N60">
-        <v>0.65402004</v>
+        <v>0.65245142</v>
       </c>
       <c r="O60">
-        <v>0.196206012</v>
+        <v>0.195735426</v>
       </c>
       <c r="P60">
-        <v>0.457814028</v>
+        <v>0.456715994</v>
       </c>
       <c r="Q60">
-        <v>0.565814028</v>
+        <v>0.5647159940000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2770491748991493</v>
+        <v>0.281829025558495</v>
       </c>
       <c r="T60">
-        <v>1.612371587839885</v>
+        <v>1.645698821982917</v>
       </c>
       <c r="U60">
         <v>0.0535</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>8.188616482135188</v>
+        <v>8.049826372268489</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.137645400478983</v>
+        <v>0.1372091475003233</v>
       </c>
       <c r="C61">
-        <v>1.886508070911003</v>
+        <v>1.871765232282221</v>
       </c>
       <c r="D61">
-        <v>3.054388070911003</v>
+        <v>3.068965232282221</v>
       </c>
       <c r="E61">
-        <v>1.52788</v>
+        <v>1.5572</v>
       </c>
       <c r="F61">
-        <v>1.72988</v>
+        <v>1.7592</v>
       </c>
       <c r="G61">
         <v>0.5620000000000001</v>
@@ -6417,28 +6417,28 @@
         <v>0.745</v>
       </c>
       <c r="M61">
-        <v>0.09254857999999999</v>
+        <v>0.0941172</v>
       </c>
       <c r="N61">
-        <v>0.65245142</v>
+        <v>0.6508828</v>
       </c>
       <c r="O61">
-        <v>0.195735426</v>
+        <v>0.19526484</v>
       </c>
       <c r="P61">
-        <v>0.456715994</v>
+        <v>0.45561796</v>
       </c>
       <c r="Q61">
-        <v>0.5647159940000001</v>
+        <v>0.56361796</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.281829025558495</v>
+        <v>0.2868478687508081</v>
       </c>
       <c r="T61">
-        <v>1.645698821982917</v>
+        <v>1.680692417833101</v>
       </c>
       <c r="U61">
         <v>0.0535</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>8.049826372268489</v>
+        <v>7.915662599397347</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1372091475003233</v>
+        <v>0.1367728945216635</v>
       </c>
       <c r="C62">
-        <v>1.871765232282221</v>
+        <v>1.857162200792742</v>
       </c>
       <c r="D62">
-        <v>3.068965232282221</v>
+        <v>3.083682200792741</v>
       </c>
       <c r="E62">
-        <v>1.5572</v>
+        <v>1.58652</v>
       </c>
       <c r="F62">
-        <v>1.7592</v>
+        <v>1.78852</v>
       </c>
       <c r="G62">
         <v>0.5620000000000001</v>
@@ -6499,28 +6499,28 @@
         <v>0.745</v>
       </c>
       <c r="M62">
-        <v>0.0941172</v>
+        <v>0.09568581999999999</v>
       </c>
       <c r="N62">
-        <v>0.6508828</v>
+        <v>0.64931418</v>
       </c>
       <c r="O62">
-        <v>0.19526484</v>
+        <v>0.194794254</v>
       </c>
       <c r="P62">
-        <v>0.45561796</v>
+        <v>0.454519926</v>
       </c>
       <c r="Q62">
-        <v>0.56361796</v>
+        <v>0.562519926</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.2868478687508081</v>
+        <v>0.292124088517086</v>
       </c>
       <c r="T62">
-        <v>1.680692417833101</v>
+        <v>1.717480557060217</v>
       </c>
       <c r="U62">
         <v>0.0535</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>7.915662599397347</v>
+        <v>7.785897638751489</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1367728945216635</v>
+        <v>0.1363366415430038</v>
       </c>
       <c r="C63">
-        <v>1.857162200792742</v>
+        <v>1.842700997434725</v>
       </c>
       <c r="D63">
-        <v>3.083682200792741</v>
+        <v>3.098540997434725</v>
       </c>
       <c r="E63">
-        <v>1.58652</v>
+        <v>1.61584</v>
       </c>
       <c r="F63">
-        <v>1.78852</v>
+        <v>1.81784</v>
       </c>
       <c r="G63">
         <v>0.5620000000000001</v>
@@ -6581,28 +6581,28 @@
         <v>0.745</v>
       </c>
       <c r="M63">
-        <v>0.09568581999999999</v>
+        <v>0.09725444</v>
       </c>
       <c r="N63">
-        <v>0.64931418</v>
+        <v>0.6477455599999999</v>
       </c>
       <c r="O63">
-        <v>0.194794254</v>
+        <v>0.194323668</v>
       </c>
       <c r="P63">
-        <v>0.454519926</v>
+        <v>0.4534218919999999</v>
       </c>
       <c r="Q63">
-        <v>0.562519926</v>
+        <v>0.5614218919999999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.292124088517086</v>
+        <v>0.2976780040605364</v>
       </c>
       <c r="T63">
-        <v>1.717480557060217</v>
+        <v>1.756204914141392</v>
       </c>
       <c r="U63">
         <v>0.0535</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>7.785897638751489</v>
+        <v>7.660318644578077</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1363366415430038</v>
+        <v>0.1362531885643441</v>
       </c>
       <c r="C64">
-        <v>1.842700997434725</v>
+        <v>1.816239741054927</v>
       </c>
       <c r="D64">
-        <v>3.098540997434725</v>
+        <v>3.101399741054927</v>
       </c>
       <c r="E64">
-        <v>1.61584</v>
+        <v>1.64516</v>
       </c>
       <c r="F64">
-        <v>1.81784</v>
+        <v>1.84716</v>
       </c>
       <c r="G64">
         <v>0.5620000000000001</v>
@@ -6663,45 +6663,45 @@
         <v>0.745</v>
       </c>
       <c r="M64">
-        <v>0.09725444</v>
+        <v>0.100300788</v>
       </c>
       <c r="N64">
-        <v>0.6477455599999999</v>
+        <v>0.644699212</v>
       </c>
       <c r="O64">
-        <v>0.194323668</v>
+        <v>0.1934097636</v>
       </c>
       <c r="P64">
-        <v>0.4534218919999999</v>
+        <v>0.4512894484</v>
       </c>
       <c r="Q64">
-        <v>0.5614218919999999</v>
+        <v>0.5592894484000001</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2976780040605364</v>
+        <v>0.3035321312549841</v>
       </c>
       <c r="T64">
-        <v>1.756204914141392</v>
+        <v>1.797022479713441</v>
       </c>
       <c r="U64">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V64">
         <v>0.3</v>
       </c>
       <c r="W64">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y64">
-        <v>7.660318644578077</v>
+        <v>7.42765849456736</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1362531885643441</v>
+        <v>0.1358225355856844</v>
       </c>
       <c r="C65">
-        <v>1.816239741054927</v>
+        <v>1.801756326447797</v>
       </c>
       <c r="D65">
-        <v>3.101399741054927</v>
+        <v>3.116236326447797</v>
       </c>
       <c r="E65">
-        <v>1.64516</v>
+        <v>1.67448</v>
       </c>
       <c r="F65">
-        <v>1.84716</v>
+        <v>1.87648</v>
       </c>
       <c r="G65">
         <v>0.5620000000000001</v>
@@ -6745,28 +6745,28 @@
         <v>0.745</v>
       </c>
       <c r="M65">
-        <v>0.100300788</v>
+        <v>0.101892864</v>
       </c>
       <c r="N65">
-        <v>0.644699212</v>
+        <v>0.643107136</v>
       </c>
       <c r="O65">
-        <v>0.1934097636</v>
+        <v>0.1929321408</v>
       </c>
       <c r="P65">
-        <v>0.4512894484</v>
+        <v>0.4501749952</v>
       </c>
       <c r="Q65">
-        <v>0.5592894484000001</v>
+        <v>0.5581749952</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3035321312549841</v>
+        <v>0.3097114877380123</v>
       </c>
       <c r="T65">
-        <v>1.797022479713441</v>
+        <v>1.840107687817271</v>
       </c>
       <c r="U65">
         <v>0.0543</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>7.42765849456736</v>
+        <v>7.311601330589746</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1358225355856844</v>
+        <v>0.1353918826070247</v>
       </c>
       <c r="C66">
-        <v>1.801756326447797</v>
+        <v>1.787415545737997</v>
       </c>
       <c r="D66">
-        <v>3.116236326447797</v>
+        <v>3.131215545737997</v>
       </c>
       <c r="E66">
-        <v>1.67448</v>
+        <v>1.7038</v>
       </c>
       <c r="F66">
-        <v>1.87648</v>
+        <v>1.9058</v>
       </c>
       <c r="G66">
         <v>0.5620000000000001</v>
@@ -6827,28 +6827,28 @@
         <v>0.745</v>
       </c>
       <c r="M66">
-        <v>0.101892864</v>
+        <v>0.10348494</v>
       </c>
       <c r="N66">
-        <v>0.643107136</v>
+        <v>0.64151506</v>
       </c>
       <c r="O66">
-        <v>0.1929321408</v>
+        <v>0.192454518</v>
       </c>
       <c r="P66">
-        <v>0.4501749952</v>
+        <v>0.449060542</v>
       </c>
       <c r="Q66">
-        <v>0.5581749952</v>
+        <v>0.557060542</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3097114877380123</v>
+        <v>0.3162439503057848</v>
       </c>
       <c r="T66">
-        <v>1.840107687817271</v>
+        <v>1.885654907812747</v>
       </c>
       <c r="U66">
         <v>0.0543</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>7.311601330589746</v>
+        <v>7.199115156272981</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1353918826070247</v>
+        <v>0.1349612296283649</v>
       </c>
       <c r="C67">
-        <v>1.787415545737997</v>
+        <v>1.773219465711043</v>
       </c>
       <c r="D67">
-        <v>3.131215545737997</v>
+        <v>3.146339465711042</v>
       </c>
       <c r="E67">
-        <v>1.7038</v>
+        <v>1.73312</v>
       </c>
       <c r="F67">
-        <v>1.9058</v>
+        <v>1.93512</v>
       </c>
       <c r="G67">
         <v>0.5620000000000001</v>
@@ -6909,28 +6909,28 @@
         <v>0.745</v>
       </c>
       <c r="M67">
-        <v>0.10348494</v>
+        <v>0.105077016</v>
       </c>
       <c r="N67">
-        <v>0.64151506</v>
+        <v>0.639922984</v>
       </c>
       <c r="O67">
-        <v>0.192454518</v>
+        <v>0.1919768952</v>
       </c>
       <c r="P67">
-        <v>0.449060542</v>
+        <v>0.4479460888</v>
       </c>
       <c r="Q67">
-        <v>0.557060542</v>
+        <v>0.5559460888000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3162439503057848</v>
+        <v>0.323160675377544</v>
       </c>
       <c r="T67">
-        <v>1.885654907812747</v>
+        <v>1.933881376043253</v>
       </c>
       <c r="U67">
         <v>0.0543</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>7.199115156272981</v>
+        <v>7.090037653905209</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1349612296283649</v>
+        <v>0.1345305766497052</v>
       </c>
       <c r="C68">
-        <v>1.773219465711043</v>
+        <v>1.759170193276943</v>
       </c>
       <c r="D68">
-        <v>3.146339465711042</v>
+        <v>3.161610193276944</v>
       </c>
       <c r="E68">
-        <v>1.73312</v>
+        <v>1.76244</v>
       </c>
       <c r="F68">
-        <v>1.93512</v>
+        <v>1.96444</v>
       </c>
       <c r="G68">
         <v>0.5620000000000001</v>
@@ -6991,28 +6991,28 @@
         <v>0.745</v>
       </c>
       <c r="M68">
-        <v>0.105077016</v>
+        <v>0.106669092</v>
       </c>
       <c r="N68">
-        <v>0.639922984</v>
+        <v>0.638330908</v>
       </c>
       <c r="O68">
-        <v>0.1919768952</v>
+        <v>0.1914992724</v>
       </c>
       <c r="P68">
-        <v>0.4479460888</v>
+        <v>0.4468316356000001</v>
       </c>
       <c r="Q68">
-        <v>0.5559460888000001</v>
+        <v>0.5548316356</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.323160675377544</v>
+        <v>0.3304965959081977</v>
       </c>
       <c r="T68">
-        <v>1.933881376043253</v>
+        <v>1.985030660530152</v>
       </c>
       <c r="U68">
         <v>0.0543</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>7.090037653905209</v>
+        <v>6.984216196384234</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1345305766497052</v>
+        <v>0.1340999236710455</v>
       </c>
       <c r="C69">
-        <v>1.759170193276943</v>
+        <v>1.745269876448676</v>
       </c>
       <c r="D69">
-        <v>3.161610193276944</v>
+        <v>3.177029876448677</v>
       </c>
       <c r="E69">
-        <v>1.76244</v>
+        <v>1.79176</v>
       </c>
       <c r="F69">
-        <v>1.96444</v>
+        <v>1.99376</v>
       </c>
       <c r="G69">
         <v>0.5620000000000001</v>
@@ -7073,28 +7073,28 @@
         <v>0.745</v>
       </c>
       <c r="M69">
-        <v>0.106669092</v>
+        <v>0.108261168</v>
       </c>
       <c r="N69">
-        <v>0.638330908</v>
+        <v>0.636738832</v>
       </c>
       <c r="O69">
-        <v>0.1914992724</v>
+        <v>0.1910216496</v>
       </c>
       <c r="P69">
-        <v>0.4468316356000001</v>
+        <v>0.4457171824</v>
       </c>
       <c r="Q69">
-        <v>0.5548316356</v>
+        <v>0.5537171824</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3304965959081977</v>
+        <v>0.3382910114720173</v>
       </c>
       <c r="T69">
-        <v>1.985030660530152</v>
+        <v>2.039376775297483</v>
       </c>
       <c r="U69">
         <v>0.0543</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>6.984216196384234</v>
+        <v>6.881507134672701</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1340999236710455</v>
+        <v>0.1336692706923858</v>
       </c>
       <c r="C70">
-        <v>1.745269876448676</v>
+        <v>1.731520705349411</v>
       </c>
       <c r="D70">
-        <v>3.177029876448677</v>
+        <v>3.192600705349411</v>
       </c>
       <c r="E70">
-        <v>1.79176</v>
+        <v>1.82108</v>
       </c>
       <c r="F70">
-        <v>1.99376</v>
+        <v>2.02308</v>
       </c>
       <c r="G70">
         <v>0.5620000000000001</v>
@@ -7155,28 +7155,28 @@
         <v>0.745</v>
       </c>
       <c r="M70">
-        <v>0.108261168</v>
+        <v>0.109853244</v>
       </c>
       <c r="N70">
-        <v>0.636738832</v>
+        <v>0.6351467559999999</v>
       </c>
       <c r="O70">
-        <v>0.1910216496</v>
+        <v>0.1905440268</v>
       </c>
       <c r="P70">
-        <v>0.4457171824</v>
+        <v>0.4446027292</v>
       </c>
       <c r="Q70">
-        <v>0.5537171824</v>
+        <v>0.5526027292</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3382910114720173</v>
+        <v>0.3465882925560833</v>
       </c>
       <c r="T70">
-        <v>2.039376775297483</v>
+        <v>2.097229091017544</v>
       </c>
       <c r="U70">
         <v>0.0543</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>6.881507134672701</v>
+        <v>6.781775147213676</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1336692706923858</v>
+        <v>0.1332386177137261</v>
       </c>
       <c r="C71">
-        <v>1.731520705349411</v>
+        <v>1.717924913249532</v>
       </c>
       <c r="D71">
-        <v>3.192600705349411</v>
+        <v>3.208324913249533</v>
       </c>
       <c r="E71">
-        <v>1.82108</v>
+        <v>1.8504</v>
       </c>
       <c r="F71">
-        <v>2.02308</v>
+        <v>2.0524</v>
       </c>
       <c r="G71">
         <v>0.5620000000000001</v>
@@ -7237,28 +7237,28 @@
         <v>0.745</v>
       </c>
       <c r="M71">
-        <v>0.109853244</v>
+        <v>0.11144532</v>
       </c>
       <c r="N71">
-        <v>0.6351467559999999</v>
+        <v>0.63355468</v>
       </c>
       <c r="O71">
-        <v>0.1905440268</v>
+        <v>0.190066404</v>
       </c>
       <c r="P71">
-        <v>0.4446027292</v>
+        <v>0.4434882760000001</v>
       </c>
       <c r="Q71">
-        <v>0.5526027292</v>
+        <v>0.5514882760000001</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3465882925560833</v>
+        <v>0.3554387257124204</v>
       </c>
       <c r="T71">
-        <v>2.097229091017544</v>
+        <v>2.15893822778561</v>
       </c>
       <c r="U71">
         <v>0.0543</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>6.781775147213676</v>
+        <v>6.684892645110625</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1332386177137261</v>
+        <v>0.1328079647350664</v>
       </c>
       <c r="C72">
-        <v>1.717924913249532</v>
+        <v>1.704484777634434</v>
       </c>
       <c r="D72">
-        <v>3.208324913249533</v>
+        <v>3.224204777634434</v>
       </c>
       <c r="E72">
-        <v>1.8504</v>
+        <v>1.87972</v>
       </c>
       <c r="F72">
-        <v>2.0524</v>
+        <v>2.08172</v>
       </c>
       <c r="G72">
         <v>0.5620000000000001</v>
@@ -7319,28 +7319,28 @@
         <v>0.745</v>
       </c>
       <c r="M72">
-        <v>0.11144532</v>
+        <v>0.113037396</v>
       </c>
       <c r="N72">
-        <v>0.63355468</v>
+        <v>0.6319626039999999</v>
       </c>
       <c r="O72">
-        <v>0.190066404</v>
+        <v>0.1895887812</v>
       </c>
       <c r="P72">
-        <v>0.4434882760000001</v>
+        <v>0.4423738227999999</v>
       </c>
       <c r="Q72">
-        <v>0.5514882760000001</v>
+        <v>0.5503738227999999</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3554387257124204</v>
+        <v>0.3648995335691945</v>
       </c>
       <c r="T72">
-        <v>2.15893822778561</v>
+        <v>2.224903167089404</v>
       </c>
       <c r="U72">
         <v>0.0543</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>6.684892645110625</v>
+        <v>6.590739227573854</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1328079647350664</v>
+        <v>0.1323773117564067</v>
       </c>
       <c r="C73">
-        <v>1.704484777634434</v>
+        <v>1.691202621304192</v>
       </c>
       <c r="D73">
-        <v>3.224204777634434</v>
+        <v>3.240242621304191</v>
       </c>
       <c r="E73">
-        <v>1.87972</v>
+        <v>1.90904</v>
       </c>
       <c r="F73">
-        <v>2.08172</v>
+        <v>2.11104</v>
       </c>
       <c r="G73">
         <v>0.5620000000000001</v>
@@ -7401,28 +7401,28 @@
         <v>0.745</v>
       </c>
       <c r="M73">
-        <v>0.113037396</v>
+        <v>0.114629472</v>
       </c>
       <c r="N73">
-        <v>0.631962604</v>
+        <v>0.630370528</v>
       </c>
       <c r="O73">
-        <v>0.1895887812</v>
+        <v>0.1891111584</v>
       </c>
       <c r="P73">
-        <v>0.4423738228</v>
+        <v>0.4412593696</v>
       </c>
       <c r="Q73">
-        <v>0.5503738228</v>
+        <v>0.5492593696</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3648995335691944</v>
+        <v>0.375036113415738</v>
       </c>
       <c r="T73">
-        <v>2.224903167089403</v>
+        <v>2.29557988777204</v>
       </c>
       <c r="U73">
         <v>0.0543</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>6.590739227573857</v>
+        <v>6.49920118274644</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1323773117564067</v>
+        <v>0.1319466587777469</v>
       </c>
       <c r="C74">
-        <v>1.691202621304192</v>
+        <v>1.678080813506224</v>
       </c>
       <c r="D74">
-        <v>3.240242621304191</v>
+        <v>3.256440813506224</v>
       </c>
       <c r="E74">
-        <v>1.90904</v>
+        <v>1.93836</v>
       </c>
       <c r="F74">
-        <v>2.11104</v>
+        <v>2.14036</v>
       </c>
       <c r="G74">
         <v>0.5620000000000001</v>
@@ -7483,28 +7483,28 @@
         <v>0.745</v>
       </c>
       <c r="M74">
-        <v>0.114629472</v>
+        <v>0.116221548</v>
       </c>
       <c r="N74">
-        <v>0.630370528</v>
+        <v>0.628778452</v>
       </c>
       <c r="O74">
-        <v>0.1891111584</v>
+        <v>0.1886335356</v>
       </c>
       <c r="P74">
-        <v>0.4412593696</v>
+        <v>0.4401449164</v>
       </c>
       <c r="Q74">
-        <v>0.5492593696</v>
+        <v>0.5481449164000001</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.375036113415738</v>
+        <v>0.3859235510286923</v>
       </c>
       <c r="T74">
-        <v>2.29557988777204</v>
+        <v>2.371491921097835</v>
       </c>
       <c r="U74">
         <v>0.0543</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>6.49920118274644</v>
+        <v>6.410171029558134</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1319466587777469</v>
+        <v>0.1315160057990872</v>
       </c>
       <c r="C75">
-        <v>1.678080813506224</v>
+        <v>1.665121771102087</v>
       </c>
       <c r="D75">
-        <v>3.256440813506224</v>
+        <v>3.272801771102087</v>
       </c>
       <c r="E75">
-        <v>1.93836</v>
+        <v>1.96768</v>
       </c>
       <c r="F75">
-        <v>2.14036</v>
+        <v>2.16968</v>
       </c>
       <c r="G75">
         <v>0.5620000000000001</v>
@@ -7565,28 +7565,28 @@
         <v>0.745</v>
       </c>
       <c r="M75">
-        <v>0.116221548</v>
+        <v>0.117813624</v>
       </c>
       <c r="N75">
-        <v>0.628778452</v>
+        <v>0.627186376</v>
       </c>
       <c r="O75">
-        <v>0.1886335356</v>
+        <v>0.1881559128</v>
       </c>
       <c r="P75">
-        <v>0.4401449164</v>
+        <v>0.4390304632000001</v>
       </c>
       <c r="Q75">
-        <v>0.5481449164000001</v>
+        <v>0.5470304632</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.3859235510286923</v>
+        <v>0.3976484838426431</v>
       </c>
       <c r="T75">
-        <v>2.371491921097835</v>
+        <v>2.453243341602537</v>
       </c>
       <c r="U75">
         <v>0.0543</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>6.410171029558134</v>
+        <v>6.323547096726267</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1315160057990872</v>
+        <v>0.1310853528204275</v>
       </c>
       <c r="C76">
-        <v>1.665121771102087</v>
+        <v>1.652327959769623</v>
       </c>
       <c r="D76">
-        <v>3.272801771102087</v>
+        <v>3.289327959769623</v>
       </c>
       <c r="E76">
-        <v>1.96768</v>
+        <v>1.997</v>
       </c>
       <c r="F76">
-        <v>2.16968</v>
+        <v>2.199</v>
       </c>
       <c r="G76">
         <v>0.5620000000000001</v>
@@ -7647,28 +7647,28 @@
         <v>0.745</v>
       </c>
       <c r="M76">
-        <v>0.117813624</v>
+        <v>0.1194057</v>
       </c>
       <c r="N76">
-        <v>0.627186376</v>
+        <v>0.6255943</v>
       </c>
       <c r="O76">
-        <v>0.1881559128</v>
+        <v>0.18767829</v>
       </c>
       <c r="P76">
-        <v>0.4390304632000001</v>
+        <v>0.43791601</v>
       </c>
       <c r="Q76">
-        <v>0.5470304632</v>
+        <v>0.54591601</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.3976484838426431</v>
+        <v>0.4103114112817099</v>
       </c>
       <c r="T76">
-        <v>2.453243341602537</v>
+        <v>2.541534875747616</v>
       </c>
       <c r="U76">
         <v>0.0543</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>6.323547096726267</v>
+        <v>6.239233135436584</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1310853528204275</v>
+        <v>0.1306546998417678</v>
       </c>
       <c r="C77">
-        <v>1.652327959769623</v>
+        <v>1.639701895241732</v>
       </c>
       <c r="D77">
-        <v>3.289327959769623</v>
+        <v>3.306021895241732</v>
       </c>
       <c r="E77">
-        <v>1.997</v>
+        <v>2.02632</v>
       </c>
       <c r="F77">
-        <v>2.199</v>
+        <v>2.22832</v>
       </c>
       <c r="G77">
         <v>0.5620000000000001</v>
@@ -7729,28 +7729,28 @@
         <v>0.745</v>
       </c>
       <c r="M77">
-        <v>0.1194057</v>
+        <v>0.120997776</v>
       </c>
       <c r="N77">
-        <v>0.6255943</v>
+        <v>0.624002224</v>
       </c>
       <c r="O77">
-        <v>0.18767829</v>
+        <v>0.1872006672</v>
       </c>
       <c r="P77">
-        <v>0.43791601</v>
+        <v>0.4368015568</v>
       </c>
       <c r="Q77">
-        <v>0.54591601</v>
+        <v>0.5448015568000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4103114112817099</v>
+        <v>0.4240295826740324</v>
       </c>
       <c r="T77">
-        <v>2.541534875747616</v>
+        <v>2.637184037738118</v>
       </c>
       <c r="U77">
         <v>0.0543</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>6.239233135436584</v>
+        <v>6.157137962601891</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1306546998417678</v>
+        <v>0.1307630468631081</v>
       </c>
       <c r="C78">
-        <v>1.639701895241732</v>
+        <v>1.60616597269587</v>
       </c>
       <c r="D78">
-        <v>3.306021895241732</v>
+        <v>3.30180597269587</v>
       </c>
       <c r="E78">
-        <v>2.02632</v>
+        <v>2.05564</v>
       </c>
       <c r="F78">
-        <v>2.22832</v>
+        <v>2.25764</v>
       </c>
       <c r="G78">
         <v>0.5620000000000001</v>
@@ -7811,45 +7811,45 @@
         <v>0.745</v>
       </c>
       <c r="M78">
-        <v>0.120997776</v>
+        <v>0.124847492</v>
       </c>
       <c r="N78">
-        <v>0.624002224</v>
+        <v>0.620152508</v>
       </c>
       <c r="O78">
-        <v>0.1872006672</v>
+        <v>0.1860457524</v>
       </c>
       <c r="P78">
-        <v>0.4368015568</v>
+        <v>0.4341067556</v>
       </c>
       <c r="Q78">
-        <v>0.5448015568000001</v>
+        <v>0.5421067556</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.4240295826740324</v>
+        <v>0.4389406385352524</v>
       </c>
       <c r="T78">
-        <v>2.637184037738118</v>
+        <v>2.741150518162576</v>
       </c>
       <c r="U78">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V78">
         <v>0.3</v>
       </c>
       <c r="W78">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y78">
-        <v>6.157137962601891</v>
+        <v>5.967280464072118</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1307630468631081</v>
+        <v>0.1303393938844483</v>
       </c>
       <c r="C79">
-        <v>1.60616597269587</v>
+        <v>1.593392340856506</v>
       </c>
       <c r="D79">
-        <v>3.30180597269587</v>
+        <v>3.318352340856506</v>
       </c>
       <c r="E79">
-        <v>2.05564</v>
+        <v>2.08496</v>
       </c>
       <c r="F79">
-        <v>2.25764</v>
+        <v>2.28696</v>
       </c>
       <c r="G79">
         <v>0.5620000000000001</v>
@@ -7893,28 +7893,28 @@
         <v>0.745</v>
       </c>
       <c r="M79">
-        <v>0.124847492</v>
+        <v>0.126468888</v>
       </c>
       <c r="N79">
-        <v>0.620152508</v>
+        <v>0.618531112</v>
       </c>
       <c r="O79">
-        <v>0.1860457524</v>
+        <v>0.1855593336</v>
       </c>
       <c r="P79">
-        <v>0.4341067556</v>
+        <v>0.4329717784</v>
       </c>
       <c r="Q79">
-        <v>0.5421067556</v>
+        <v>0.5409717784</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.4389406385352524</v>
+        <v>0.4552072449293106</v>
       </c>
       <c r="T79">
-        <v>2.741150518162576</v>
+        <v>2.85456849680744</v>
       </c>
       <c r="U79">
         <v>0.0553</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>5.967280464072118</v>
+        <v>5.890776868378885</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1303393938844483</v>
+        <v>0.1299157409057886</v>
       </c>
       <c r="C80">
-        <v>1.593392340856506</v>
+        <v>1.580785382176808</v>
       </c>
       <c r="D80">
-        <v>3.318352340856506</v>
+        <v>3.335065382176808</v>
       </c>
       <c r="E80">
-        <v>2.08496</v>
+        <v>2.11428</v>
       </c>
       <c r="F80">
-        <v>2.28696</v>
+        <v>2.31628</v>
       </c>
       <c r="G80">
         <v>0.5620000000000001</v>
@@ -7975,28 +7975,28 @@
         <v>0.745</v>
       </c>
       <c r="M80">
-        <v>0.126468888</v>
+        <v>0.128090284</v>
       </c>
       <c r="N80">
-        <v>0.618531112</v>
+        <v>0.616909716</v>
       </c>
       <c r="O80">
-        <v>0.1855593336</v>
+        <v>0.1850729148</v>
       </c>
       <c r="P80">
-        <v>0.4329717784</v>
+        <v>0.4318368012</v>
       </c>
       <c r="Q80">
-        <v>0.5409717784</v>
+        <v>0.5398368012</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.4552072449293106</v>
+        <v>0.4730230519323268</v>
       </c>
       <c r="T80">
-        <v>2.85456849680744</v>
+        <v>2.978788187704196</v>
       </c>
       <c r="U80">
         <v>0.0553</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>5.890776868378885</v>
+        <v>5.816210072576621</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1299157409057886</v>
+        <v>0.1294920879271289</v>
       </c>
       <c r="C81">
-        <v>1.580785382176808</v>
+        <v>1.568347627777066</v>
       </c>
       <c r="D81">
-        <v>3.335065382176808</v>
+        <v>3.351947627777066</v>
       </c>
       <c r="E81">
-        <v>2.11428</v>
+        <v>2.1436</v>
       </c>
       <c r="F81">
-        <v>2.31628</v>
+        <v>2.3456</v>
       </c>
       <c r="G81">
         <v>0.5620000000000001</v>
@@ -8057,28 +8057,28 @@
         <v>0.745</v>
       </c>
       <c r="M81">
-        <v>0.128090284</v>
+        <v>0.12971168</v>
       </c>
       <c r="N81">
-        <v>0.616909716</v>
+        <v>0.61528832</v>
       </c>
       <c r="O81">
-        <v>0.1850729148</v>
+        <v>0.184586496</v>
       </c>
       <c r="P81">
-        <v>0.4318368012</v>
+        <v>0.430701824</v>
       </c>
       <c r="Q81">
-        <v>0.5398368012</v>
+        <v>0.538701824</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.4730230519323268</v>
+        <v>0.4926204396356445</v>
       </c>
       <c r="T81">
-        <v>2.978788187704196</v>
+        <v>3.115429847690627</v>
       </c>
       <c r="U81">
         <v>0.0553</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>5.816210072576621</v>
+        <v>5.743507446669413</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1294920879271289</v>
+        <v>0.1290684349484692</v>
       </c>
       <c r="C82">
-        <v>1.568347627777066</v>
+        <v>1.556081660288881</v>
       </c>
       <c r="D82">
-        <v>3.351947627777066</v>
+        <v>3.369001660288881</v>
       </c>
       <c r="E82">
-        <v>2.1436</v>
+        <v>2.17292</v>
       </c>
       <c r="F82">
-        <v>2.3456</v>
+        <v>2.37492</v>
       </c>
       <c r="G82">
         <v>0.5620000000000001</v>
@@ -8139,28 +8139,28 @@
         <v>0.745</v>
       </c>
       <c r="M82">
-        <v>0.12971168</v>
+        <v>0.131333076</v>
       </c>
       <c r="N82">
-        <v>0.61528832</v>
+        <v>0.613666924</v>
       </c>
       <c r="O82">
-        <v>0.184586496</v>
+        <v>0.1841000772</v>
       </c>
       <c r="P82">
-        <v>0.430701824</v>
+        <v>0.4295668468</v>
       </c>
       <c r="Q82">
-        <v>0.538701824</v>
+        <v>0.5375668468</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.4926204396356445</v>
+        <v>0.514280710255101</v>
       </c>
       <c r="T82">
-        <v>3.115429847690627</v>
+        <v>3.266454840307209</v>
       </c>
       <c r="U82">
         <v>0.0553</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>5.743507446669413</v>
+        <v>5.672599947327816</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1290684349484692</v>
+        <v>0.1286447819698094</v>
       </c>
       <c r="C83">
-        <v>1.556081660288881</v>
+        <v>1.543990115172269</v>
       </c>
       <c r="D83">
-        <v>3.369001660288881</v>
+        <v>3.386230115172269</v>
       </c>
       <c r="E83">
-        <v>2.17292</v>
+        <v>2.20224</v>
       </c>
       <c r="F83">
-        <v>2.37492</v>
+        <v>2.40424</v>
       </c>
       <c r="G83">
         <v>0.5620000000000001</v>
@@ -8221,28 +8221,28 @@
         <v>0.745</v>
       </c>
       <c r="M83">
-        <v>0.131333076</v>
+        <v>0.132954472</v>
       </c>
       <c r="N83">
-        <v>0.613666924</v>
+        <v>0.612045528</v>
       </c>
       <c r="O83">
-        <v>0.1841000772</v>
+        <v>0.1836136584</v>
       </c>
       <c r="P83">
-        <v>0.4295668468</v>
+        <v>0.4284318696</v>
       </c>
       <c r="Q83">
-        <v>0.5375668468</v>
+        <v>0.5364318696</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.514280710255101</v>
+        <v>0.5383476776100526</v>
       </c>
       <c r="T83">
-        <v>3.266454840307209</v>
+        <v>3.434260387658966</v>
       </c>
       <c r="U83">
         <v>0.0553</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>5.672599947327816</v>
+        <v>5.603421899189671</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1286447819698094</v>
+        <v>0.1282211289911497</v>
       </c>
       <c r="C84">
-        <v>1.543990115172269</v>
+        <v>1.532075682073372</v>
       </c>
       <c r="D84">
-        <v>3.386230115172269</v>
+        <v>3.403635682073372</v>
       </c>
       <c r="E84">
-        <v>2.20224</v>
+        <v>2.23156</v>
       </c>
       <c r="F84">
-        <v>2.40424</v>
+        <v>2.43356</v>
       </c>
       <c r="G84">
         <v>0.5620000000000001</v>
@@ -8303,28 +8303,28 @@
         <v>0.745</v>
       </c>
       <c r="M84">
-        <v>0.132954472</v>
+        <v>0.134575868</v>
       </c>
       <c r="N84">
-        <v>0.612045528</v>
+        <v>0.610424132</v>
       </c>
       <c r="O84">
-        <v>0.1836136584</v>
+        <v>0.1831272396</v>
       </c>
       <c r="P84">
-        <v>0.4284318696</v>
+        <v>0.4272968924</v>
       </c>
       <c r="Q84">
-        <v>0.5364318696</v>
+        <v>0.5352968924</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.5383476776100526</v>
+        <v>0.5652460528891162</v>
       </c>
       <c r="T84">
-        <v>3.434260387658966</v>
+        <v>3.621807764110931</v>
       </c>
       <c r="U84">
         <v>0.0553</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>5.603421899189671</v>
+        <v>5.535910791970518</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1282211289911497</v>
+        <v>0.12779747601249</v>
       </c>
       <c r="C85">
-        <v>1.532075682073372</v>
+        <v>1.520341106224273</v>
       </c>
       <c r="D85">
-        <v>3.403635682073372</v>
+        <v>3.421221106224273</v>
       </c>
       <c r="E85">
-        <v>2.23156</v>
+        <v>2.26088</v>
       </c>
       <c r="F85">
-        <v>2.43356</v>
+        <v>2.46288</v>
       </c>
       <c r="G85">
         <v>0.5620000000000001</v>
@@ -8385,28 +8385,28 @@
         <v>0.745</v>
       </c>
       <c r="M85">
-        <v>0.134575868</v>
+        <v>0.136197264</v>
       </c>
       <c r="N85">
-        <v>0.610424132</v>
+        <v>0.608802736</v>
       </c>
       <c r="O85">
-        <v>0.1831272396</v>
+        <v>0.1826408208</v>
       </c>
       <c r="P85">
-        <v>0.4272968924</v>
+        <v>0.4261619152</v>
       </c>
       <c r="Q85">
-        <v>0.5352968924</v>
+        <v>0.5341619152</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.5652460528891162</v>
+        <v>0.5955067250780628</v>
       </c>
       <c r="T85">
-        <v>3.621807764110931</v>
+        <v>3.832798562619391</v>
       </c>
       <c r="U85">
         <v>0.0553</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>5.535910791970518</v>
+        <v>5.470007092066107</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.12779747601249</v>
+        <v>0.1273738230338303</v>
       </c>
       <c r="C86">
-        <v>1.520341106224272</v>
+        <v>1.508789189886409</v>
       </c>
       <c r="D86">
-        <v>3.421221106224271</v>
+        <v>3.43898918988641</v>
       </c>
       <c r="E86">
-        <v>2.26088</v>
+        <v>2.2902</v>
       </c>
       <c r="F86">
-        <v>2.46288</v>
+        <v>2.4922</v>
       </c>
       <c r="G86">
         <v>0.5620000000000001</v>
@@ -8467,28 +8467,28 @@
         <v>0.745</v>
       </c>
       <c r="M86">
-        <v>0.136197264</v>
+        <v>0.13781866</v>
       </c>
       <c r="N86">
-        <v>0.608802736</v>
+        <v>0.60718134</v>
       </c>
       <c r="O86">
-        <v>0.1826408208</v>
+        <v>0.182154402</v>
       </c>
       <c r="P86">
-        <v>0.4261619152</v>
+        <v>0.425026938</v>
       </c>
       <c r="Q86">
-        <v>0.5341619152</v>
+        <v>0.533026938</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.5955067250780625</v>
+        <v>0.6298021535588685</v>
       </c>
       <c r="T86">
-        <v>3.832798562619388</v>
+        <v>4.071921467595643</v>
       </c>
       <c r="U86">
         <v>0.0553</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>5.470007092066108</v>
+        <v>5.405654067453566</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1273738230338303</v>
+        <v>0.1269501700551706</v>
       </c>
       <c r="C87">
-        <v>1.508789189886409</v>
+        <v>1.497422793839222</v>
       </c>
       <c r="D87">
-        <v>3.43898918988641</v>
+        <v>3.456942793839222</v>
       </c>
       <c r="E87">
-        <v>2.2902</v>
+        <v>2.31952</v>
       </c>
       <c r="F87">
-        <v>2.4922</v>
+        <v>2.52152</v>
       </c>
       <c r="G87">
         <v>0.5620000000000001</v>
@@ -8549,28 +8549,28 @@
         <v>0.745</v>
       </c>
       <c r="M87">
-        <v>0.13781866</v>
+        <v>0.139440056</v>
       </c>
       <c r="N87">
-        <v>0.60718134</v>
+        <v>0.605559944</v>
       </c>
       <c r="O87">
-        <v>0.182154402</v>
+        <v>0.1816679832</v>
       </c>
       <c r="P87">
-        <v>0.425026938</v>
+        <v>0.4238919608</v>
       </c>
       <c r="Q87">
-        <v>0.533026938</v>
+        <v>0.5318919608</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.6298021535588685</v>
+        <v>0.668996928965504</v>
       </c>
       <c r="T87">
-        <v>4.071921467595643</v>
+        <v>4.345204787568504</v>
       </c>
       <c r="U87">
         <v>0.0553</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>5.405654067453566</v>
+        <v>5.342797624808758</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1269501700551706</v>
+        <v>0.1265265170765109</v>
       </c>
       <c r="C88">
-        <v>1.497422793839222</v>
+        <v>1.486244838915663</v>
       </c>
       <c r="D88">
-        <v>3.456942793839222</v>
+        <v>3.475084838915663</v>
       </c>
       <c r="E88">
-        <v>2.31952</v>
+        <v>2.34884</v>
       </c>
       <c r="F88">
-        <v>2.52152</v>
+        <v>2.55084</v>
       </c>
       <c r="G88">
         <v>0.5620000000000001</v>
@@ -8631,28 +8631,28 @@
         <v>0.745</v>
       </c>
       <c r="M88">
-        <v>0.139440056</v>
+        <v>0.141061452</v>
       </c>
       <c r="N88">
-        <v>0.605559944</v>
+        <v>0.603938548</v>
       </c>
       <c r="O88">
-        <v>0.1816679832</v>
+        <v>0.1811815644</v>
       </c>
       <c r="P88">
-        <v>0.4238919608</v>
+        <v>0.4227569836</v>
       </c>
       <c r="Q88">
-        <v>0.5318919608</v>
+        <v>0.5307569836</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.668996928965504</v>
+        <v>0.7142216698193142</v>
       </c>
       <c r="T88">
-        <v>4.345204787568504</v>
+        <v>4.6605316952295</v>
       </c>
       <c r="U88">
         <v>0.0553</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>5.342797624808758</v>
+        <v>5.281386157856931</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1265265170765109</v>
+        <v>0.1261028640978511</v>
       </c>
       <c r="C89">
-        <v>1.486244838915663</v>
+        <v>1.47525830758632</v>
       </c>
       <c r="D89">
-        <v>3.475084838915663</v>
+        <v>3.49341830758632</v>
       </c>
       <c r="E89">
-        <v>2.34884</v>
+        <v>2.37816</v>
       </c>
       <c r="F89">
-        <v>2.55084</v>
+        <v>2.58016</v>
       </c>
       <c r="G89">
         <v>0.5620000000000001</v>
@@ -8713,28 +8713,28 @@
         <v>0.745</v>
       </c>
       <c r="M89">
-        <v>0.141061452</v>
+        <v>0.142682848</v>
       </c>
       <c r="N89">
-        <v>0.603938548</v>
+        <v>0.602317152</v>
       </c>
       <c r="O89">
-        <v>0.1811815644</v>
+        <v>0.1806951456</v>
       </c>
       <c r="P89">
-        <v>0.4227569836</v>
+        <v>0.4216220064</v>
       </c>
       <c r="Q89">
-        <v>0.5307569836</v>
+        <v>0.5296220064</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.7142216698193142</v>
+        <v>0.7669838674820928</v>
       </c>
       <c r="T89">
-        <v>4.6605316952295</v>
+        <v>5.028413087500661</v>
       </c>
       <c r="U89">
         <v>0.0553</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>5.281386157856931</v>
+        <v>5.221370406063103</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1261028640978511</v>
+        <v>0.1256792111191914</v>
       </c>
       <c r="C90">
-        <v>1.47525830758632</v>
+        <v>1.464466245593931</v>
       </c>
       <c r="D90">
-        <v>3.49341830758632</v>
+        <v>3.511946245593931</v>
       </c>
       <c r="E90">
-        <v>2.37816</v>
+        <v>2.40748</v>
       </c>
       <c r="F90">
-        <v>2.58016</v>
+        <v>2.60948</v>
       </c>
       <c r="G90">
         <v>0.5620000000000001</v>
@@ -8795,28 +8795,28 @@
         <v>0.745</v>
       </c>
       <c r="M90">
-        <v>0.142682848</v>
+        <v>0.144304244</v>
       </c>
       <c r="N90">
-        <v>0.602317152</v>
+        <v>0.600695756</v>
       </c>
       <c r="O90">
-        <v>0.1806951456</v>
+        <v>0.1802087268</v>
       </c>
       <c r="P90">
-        <v>0.4216220064</v>
+        <v>0.4204870292</v>
       </c>
       <c r="Q90">
-        <v>0.5296220064</v>
+        <v>0.5284870292</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.7669838674820928</v>
+        <v>0.8293391919926493</v>
       </c>
       <c r="T90">
-        <v>5.028413087500661</v>
+        <v>5.463182005639305</v>
       </c>
       <c r="U90">
         <v>0.0553</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>5.221370406063103</v>
+        <v>5.162703322848911</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1256792111191914</v>
+        <v>0.1252555581405317</v>
       </c>
       <c r="C91">
-        <v>1.464466245593931</v>
+        <v>1.453871763640223</v>
       </c>
       <c r="D91">
-        <v>3.511946245593931</v>
+        <v>3.530671763640223</v>
       </c>
       <c r="E91">
-        <v>2.40748</v>
+        <v>2.4368</v>
       </c>
       <c r="F91">
-        <v>2.60948</v>
+        <v>2.6388</v>
       </c>
       <c r="G91">
         <v>0.5620000000000001</v>
@@ -8877,28 +8877,28 @@
         <v>0.745</v>
       </c>
       <c r="M91">
-        <v>0.144304244</v>
+        <v>0.14592564</v>
       </c>
       <c r="N91">
-        <v>0.600695756</v>
+        <v>0.59907436</v>
       </c>
       <c r="O91">
-        <v>0.1802087268</v>
+        <v>0.179722308</v>
       </c>
       <c r="P91">
-        <v>0.4204870292</v>
+        <v>0.419352052</v>
       </c>
       <c r="Q91">
-        <v>0.5284870292</v>
+        <v>0.527352052</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.8293391919926493</v>
+        <v>0.904165581405317</v>
       </c>
       <c r="T91">
-        <v>5.463182005639305</v>
+        <v>5.984904707405677</v>
       </c>
       <c r="U91">
         <v>0.0553</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>5.162703322848911</v>
+        <v>5.105339952595035</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1252555581405317</v>
+        <v>0.124831905161872</v>
       </c>
       <c r="C92">
-        <v>1.453871763640223</v>
+        <v>1.443478039126968</v>
       </c>
       <c r="D92">
-        <v>3.530671763640223</v>
+        <v>3.549598039126968</v>
       </c>
       <c r="E92">
-        <v>2.4368</v>
+        <v>2.46612</v>
       </c>
       <c r="F92">
-        <v>2.6388</v>
+        <v>2.66812</v>
       </c>
       <c r="G92">
         <v>0.5620000000000001</v>
@@ -8959,28 +8959,28 @@
         <v>0.745</v>
       </c>
       <c r="M92">
-        <v>0.14592564</v>
+        <v>0.147547036</v>
       </c>
       <c r="N92">
-        <v>0.59907436</v>
+        <v>0.5974529639999999</v>
       </c>
       <c r="O92">
-        <v>0.179722308</v>
+        <v>0.1792358892</v>
       </c>
       <c r="P92">
-        <v>0.419352052</v>
+        <v>0.4182170747999999</v>
       </c>
       <c r="Q92">
-        <v>0.527352052</v>
+        <v>0.5262170747999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.904165581405317</v>
+        <v>0.9956200573541333</v>
       </c>
       <c r="T92">
-        <v>5.984904707405677</v>
+        <v>6.622565787342356</v>
       </c>
       <c r="U92">
         <v>0.0553</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>5.105339952595035</v>
+        <v>5.049237315753329</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.124831905161872</v>
+        <v>0.1244082521832123</v>
       </c>
       <c r="C93">
-        <v>1.443478039126968</v>
+        <v>1.433288317953368</v>
       </c>
       <c r="D93">
-        <v>3.549598039126968</v>
+        <v>3.568728317953368</v>
       </c>
       <c r="E93">
-        <v>2.46612</v>
+        <v>2.49544</v>
       </c>
       <c r="F93">
-        <v>2.66812</v>
+        <v>2.69744</v>
       </c>
       <c r="G93">
         <v>0.5620000000000001</v>
@@ -9041,28 +9041,28 @@
         <v>0.745</v>
       </c>
       <c r="M93">
-        <v>0.147547036</v>
+        <v>0.149168432</v>
       </c>
       <c r="N93">
-        <v>0.5974529639999999</v>
+        <v>0.5958315679999999</v>
       </c>
       <c r="O93">
-        <v>0.1792358892</v>
+        <v>0.1787494704</v>
       </c>
       <c r="P93">
-        <v>0.4182170747999999</v>
+        <v>0.4170820975999999</v>
       </c>
       <c r="Q93">
-        <v>0.5262170747999999</v>
+        <v>0.5250820975999999</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.9956200573541333</v>
+        <v>1.109938152290154</v>
       </c>
       <c r="T93">
-        <v>6.622565787342356</v>
+        <v>7.419642137263206</v>
       </c>
       <c r="U93">
         <v>0.0553</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>5.049237315753329</v>
+        <v>4.994354301451663</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1244082521832123</v>
+        <v>0.1239845992045525</v>
       </c>
       <c r="C94">
-        <v>1.433288317953368</v>
+        <v>1.423305916371859</v>
       </c>
       <c r="D94">
-        <v>3.568728317953368</v>
+        <v>3.588065916371859</v>
       </c>
       <c r="E94">
-        <v>2.49544</v>
+        <v>2.52476</v>
       </c>
       <c r="F94">
-        <v>2.69744</v>
+        <v>2.72676</v>
       </c>
       <c r="G94">
         <v>0.5620000000000001</v>
@@ -9123,28 +9123,28 @@
         <v>0.745</v>
       </c>
       <c r="M94">
-        <v>0.149168432</v>
+        <v>0.150789828</v>
       </c>
       <c r="N94">
-        <v>0.5958315679999999</v>
+        <v>0.5942101719999999</v>
       </c>
       <c r="O94">
-        <v>0.1787494704</v>
+        <v>0.1782630516</v>
       </c>
       <c r="P94">
-        <v>0.4170820975999999</v>
+        <v>0.4159471203999999</v>
       </c>
       <c r="Q94">
-        <v>0.5250820975999999</v>
+        <v>0.5239471203999999</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.109938152290154</v>
+        <v>1.256918560065037</v>
       </c>
       <c r="T94">
-        <v>7.419642137263206</v>
+        <v>8.44445458716144</v>
       </c>
       <c r="U94">
         <v>0.0553</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>4.994354301451663</v>
+        <v>4.940651567027452</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.1239845992045525</v>
+        <v>0.1235609462258928</v>
       </c>
       <c r="C95">
-        <v>1.423305916371859</v>
+        <v>1.413534222904581</v>
       </c>
       <c r="D95">
-        <v>3.588065916371859</v>
+        <v>3.607614222904581</v>
       </c>
       <c r="E95">
-        <v>2.52476</v>
+        <v>2.55408</v>
       </c>
       <c r="F95">
-        <v>2.72676</v>
+        <v>2.75608</v>
       </c>
       <c r="G95">
         <v>0.5620000000000001</v>
@@ -9205,28 +9205,28 @@
         <v>0.745</v>
       </c>
       <c r="M95">
-        <v>0.150789828</v>
+        <v>0.152411224</v>
       </c>
       <c r="N95">
-        <v>0.5942101719999999</v>
+        <v>0.5925887759999999</v>
       </c>
       <c r="O95">
-        <v>0.1782630516</v>
+        <v>0.1777766328</v>
       </c>
       <c r="P95">
-        <v>0.4159471203999999</v>
+        <v>0.4148121431999999</v>
       </c>
       <c r="Q95">
-        <v>0.5239471203999999</v>
+        <v>0.5228121431999999</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.256918560065037</v>
+        <v>1.452892437098215</v>
       </c>
       <c r="T95">
-        <v>8.44445458716144</v>
+        <v>9.810871187025754</v>
       </c>
       <c r="U95">
         <v>0.0553</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>4.940651567027452</v>
+        <v>4.888091443973968</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1235609462258928</v>
+        <v>0.1231372932472331</v>
       </c>
       <c r="C96">
-        <v>1.413534222904581</v>
+        <v>1.403976700322854</v>
       </c>
       <c r="D96">
-        <v>3.607614222904581</v>
+        <v>3.627376700322854</v>
       </c>
       <c r="E96">
-        <v>2.55408</v>
+        <v>2.5834</v>
       </c>
       <c r="F96">
-        <v>2.75608</v>
+        <v>2.7854</v>
       </c>
       <c r="G96">
         <v>0.5620000000000001</v>
@@ -9287,28 +9287,28 @@
         <v>0.745</v>
       </c>
       <c r="M96">
-        <v>0.152411224</v>
+        <v>0.15403262</v>
       </c>
       <c r="N96">
-        <v>0.5925887759999999</v>
+        <v>0.5909673799999999</v>
       </c>
       <c r="O96">
-        <v>0.1777766328</v>
+        <v>0.177290214</v>
       </c>
       <c r="P96">
-        <v>0.4148121431999999</v>
+        <v>0.4136771659999999</v>
       </c>
       <c r="Q96">
-        <v>0.5228121431999999</v>
+        <v>0.5216771659999999</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.452892437098215</v>
+        <v>1.727255864944664</v>
       </c>
       <c r="T96">
-        <v>9.810871187025754</v>
+        <v>11.72385442683579</v>
       </c>
       <c r="U96">
         <v>0.0553</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>4.888091443973968</v>
+        <v>4.836637849826873</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1231372932472331</v>
+        <v>0.1227136402685734</v>
       </c>
       <c r="C97">
-        <v>1.403976700322854</v>
+        <v>1.394636887692045</v>
       </c>
       <c r="D97">
-        <v>3.627376700322854</v>
+        <v>3.647356887692045</v>
       </c>
       <c r="E97">
-        <v>2.5834</v>
+        <v>2.61272</v>
       </c>
       <c r="F97">
-        <v>2.7854</v>
+        <v>2.81472</v>
       </c>
       <c r="G97">
         <v>0.5620000000000001</v>
@@ -9369,28 +9369,28 @@
         <v>0.745</v>
       </c>
       <c r="M97">
-        <v>0.15403262</v>
+        <v>0.155654016</v>
       </c>
       <c r="N97">
-        <v>0.5909673799999999</v>
+        <v>0.5893459839999999</v>
       </c>
       <c r="O97">
-        <v>0.177290214</v>
+        <v>0.1768037952</v>
       </c>
       <c r="P97">
-        <v>0.4136771659999999</v>
+        <v>0.4125421887999999</v>
       </c>
       <c r="Q97">
-        <v>0.5216771659999999</v>
+        <v>0.5205421887999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.727255864944664</v>
+        <v>2.138801006714338</v>
       </c>
       <c r="T97">
-        <v>11.72385442683579</v>
+        <v>14.59332928655085</v>
       </c>
       <c r="U97">
         <v>0.0553</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>4.836637849826873</v>
+        <v>4.786256205557843</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1227136402685734</v>
+        <v>0.1222899872899137</v>
       </c>
       <c r="C98">
-        <v>1.394636887692044</v>
+        <v>1.385518402484419</v>
       </c>
       <c r="D98">
-        <v>3.647356887692044</v>
+        <v>3.667558402484419</v>
       </c>
       <c r="E98">
-        <v>2.61272</v>
+        <v>2.64204</v>
       </c>
       <c r="F98">
-        <v>2.81472</v>
+        <v>2.84404</v>
       </c>
       <c r="G98">
         <v>0.5620000000000001</v>
@@ -9451,28 +9451,28 @@
         <v>0.745</v>
       </c>
       <c r="M98">
-        <v>0.155654016</v>
+        <v>0.157275412</v>
       </c>
       <c r="N98">
-        <v>0.5893459839999999</v>
+        <v>0.587724588</v>
       </c>
       <c r="O98">
-        <v>0.1768037952</v>
+        <v>0.1763173764</v>
       </c>
       <c r="P98">
-        <v>0.4125421887999999</v>
+        <v>0.4114072116</v>
       </c>
       <c r="Q98">
-        <v>0.5205421887999999</v>
+        <v>0.5194072116</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.138801006714333</v>
+        <v>2.824709576330453</v>
       </c>
       <c r="T98">
-        <v>14.59332928655082</v>
+        <v>19.3757873860759</v>
       </c>
       <c r="U98">
         <v>0.0553</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>4.786256205557844</v>
+        <v>4.736913358077867</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1222899872899137</v>
+        <v>0.1218663343112539</v>
       </c>
       <c r="C99">
-        <v>1.385518402484419</v>
+        <v>1.376624942762582</v>
       </c>
       <c r="D99">
-        <v>3.667558402484419</v>
+        <v>3.687984942762582</v>
       </c>
       <c r="E99">
-        <v>2.64204</v>
+        <v>2.67136</v>
       </c>
       <c r="F99">
-        <v>2.84404</v>
+        <v>2.87336</v>
       </c>
       <c r="G99">
         <v>0.5620000000000001</v>
@@ -9533,28 +9533,28 @@
         <v>0.745</v>
       </c>
       <c r="M99">
-        <v>0.157275412</v>
+        <v>0.158896808</v>
       </c>
       <c r="N99">
-        <v>0.587724588</v>
+        <v>0.5861031919999999</v>
       </c>
       <c r="O99">
-        <v>0.1763173764</v>
+        <v>0.1758309576</v>
       </c>
       <c r="P99">
-        <v>0.4114072116</v>
+        <v>0.4102722343999999</v>
       </c>
       <c r="Q99">
-        <v>0.5194072116</v>
+        <v>0.5182722343999999</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.824709576330453</v>
+        <v>4.196526715562693</v>
       </c>
       <c r="T99">
-        <v>19.3757873860759</v>
+        <v>28.94070358512606</v>
       </c>
       <c r="U99">
         <v>0.0553</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>4.736913358077867</v>
+        <v>4.688577507485235</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1218663343112539</v>
+        <v>0.1214426813325942</v>
       </c>
       <c r="C100">
-        <v>1.376624942762582</v>
+        <v>1.367960289436291</v>
       </c>
       <c r="D100">
-        <v>3.687984942762582</v>
+        <v>3.70864028943629</v>
       </c>
       <c r="E100">
-        <v>2.67136</v>
+        <v>2.70068</v>
       </c>
       <c r="F100">
-        <v>2.87336</v>
+        <v>2.90268</v>
       </c>
       <c r="G100">
         <v>0.5620000000000001</v>
@@ -9615,28 +9615,28 @@
         <v>0.745</v>
       </c>
       <c r="M100">
-        <v>0.158896808</v>
+        <v>0.160518204</v>
       </c>
       <c r="N100">
-        <v>0.5861031919999999</v>
+        <v>0.5844817959999999</v>
       </c>
       <c r="O100">
-        <v>0.1758309576</v>
+        <v>0.1753445388</v>
       </c>
       <c r="P100">
-        <v>0.4102722343999999</v>
+        <v>0.4091372571999999</v>
       </c>
       <c r="Q100">
-        <v>0.5182722343999999</v>
+        <v>0.5171372571999999</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>4.196526715562693</v>
+        <v>8.311978133259416</v>
       </c>
       <c r="T100">
-        <v>28.94070358512606</v>
+        <v>57.63545218227654</v>
       </c>
       <c r="U100">
         <v>0.0553</v>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>4.688577507485235</v>
+        <v>4.641218138722758</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1214426813325942</v>
-      </c>
-      <c r="C101">
-        <v>1.367960289436291</v>
-      </c>
-      <c r="D101">
-        <v>3.70864028943629</v>
-      </c>
-      <c r="E101">
-        <v>2.70068</v>
-      </c>
-      <c r="F101">
-        <v>2.90268</v>
-      </c>
-      <c r="G101">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="H101">
-        <v>2.73</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0.853</v>
-      </c>
-      <c r="K101">
-        <v>0.108</v>
-      </c>
-      <c r="L101">
-        <v>0.745</v>
-      </c>
-      <c r="M101">
-        <v>0.160518204</v>
-      </c>
-      <c r="N101">
-        <v>0.5844817959999999</v>
-      </c>
-      <c r="O101">
-        <v>0.1753445388</v>
-      </c>
-      <c r="P101">
-        <v>0.4091372571999999</v>
-      </c>
-      <c r="Q101">
-        <v>0.5171372571999999</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>8.311978133259416</v>
-      </c>
-      <c r="T101">
-        <v>57.63545218227654</v>
-      </c>
-      <c r="U101">
-        <v>0.0553</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.03871</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>A3/A-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>4.641218138722758</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
